--- a/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
+++ b/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
@@ -24448,7 +24448,7 @@
     "merchantname": "MERCHANT_TEST",
     "mcc": "5999",
     "posentrymode": "C",
-    "transactionamount": 833.33,
+    "transactionamount": 834,
     "transactiontype": "M",
     "terminalid": "T119",
     "userindicator02": "D",
@@ -24496,7 +24496,7 @@
       </c>
       <c r="P117" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DGCAPNMU5N9N0TL</t>
+          <t>1785306600000115C267DX4XT539GHHWOZP</t>
         </is>
       </c>
       <c r="Q117" s="38" t="inlineStr">
@@ -25146,7 +25146,7 @@
    }
   },
   {
-   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqDecline",
+   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
    "批量生成数量": 20,
    "时间窗口": "近90天",
    "bizid规则": "BIZ_ACQ_RS4_000021_0123_G2_H001~H020",
@@ -25156,7 +25156,7 @@
     "apiModel": 20,
     "bizid": "BIZ_ACQ_RS4_000021_0123_G2_H{序号001-020}",
     "biztime": "2026-07-27 14:30:00",
-    "policyCode": "Acq_Decline",
+    "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
@@ -25173,7 +25173,9 @@
     "userdata24": "D",
     "userdata27": "V",
     "userdata19": "5212340000000005",
-    "customeracctnumber": "5212340000000005"
+    "customeracctnumber": "5212340000000005",
+    "decisioncode": "D",
+    "eventtype": "AcqAuthorization"
    }
   }
  ],
@@ -25213,7 +25215,7 @@
       </c>
       <c r="P121" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DSY4Z5UFBTVMI7H</t>
+          <t>1785306600000115C267DXNX1T7UFVR1MVX</t>
         </is>
       </c>
       <c r="Q121" s="38" t="inlineStr">
@@ -26251,138 +26253,25 @@
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
    "时间窗口": "90天",
-   "请求参数": {
+   "批量生成数量": 5,
+   "分散天数": 5,
+   "字段分布说明": "基准5天各1笔×1000（日最大金额=1000，日最大笔数=1）",
+   "请求参数模板": {
     "apiModel": 20,
     "bizid": "BIZ_ACQ_RS4_000022_0128_G1_H001",
-    "biztime": "2026-07-27 14:30:00",
+    "biztime": "2026-07-26 14:30:00",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-27",
+    "transactiondate": "2026-07-26",
     "transactiontime": "14:30:00",
     "externaltransactionid": "EXT_BIZ_ACQ_RS4_000022_0128_G1_H001",
     "merchantid": "M001",
     "merchantname": "MERCHANT_TEST",
     "mcc": "5999",
     "posentrymode": "C",
-    "transactionamount": 400,
-    "transactiontype": "M",
-    "terminalid": "T128",
-    "userindicator02": "D",
-    "authsecondaryverify": "V",
-    "cvvverifycode": "V",
-    "paymentinstrumentid": "5212340000000005",
-    "customeracctnumber": "5212340000000005",
-    "transactioncategory": "M"
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
-   "时间窗口": "90天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000022_0128_G1_H002",
-    "biztime": "2026-07-27 14:30:00",
-    "policyCode": "Acq_Authorization",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-27",
-    "transactiontime": "14:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000022_0128_G1_H002",
-    "merchantid": "M001",
-    "merchantname": "MERCHANT_TEST",
-    "mcc": "5999",
-    "posentrymode": "C",
-    "transactionamount": 400,
-    "transactiontype": "M",
-    "terminalid": "T128",
-    "userindicator02": "D",
-    "authsecondaryverify": "V",
-    "cvvverifycode": "V",
-    "paymentinstrumentid": "5212340000000005",
-    "customeracctnumber": "5212340000000005",
-    "transactioncategory": "M"
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
-   "时间窗口": "90天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000022_0128_G1_H003",
-    "biztime": "2026-07-27 14:30:00",
-    "policyCode": "Acq_Authorization",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-27",
-    "transactiontime": "14:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000022_0128_G1_H003",
-    "merchantid": "M001",
-    "merchantname": "MERCHANT_TEST",
-    "mcc": "5999",
-    "posentrymode": "C",
-    "transactionamount": 400,
-    "transactiontype": "M",
-    "terminalid": "T128",
-    "userindicator02": "D",
-    "authsecondaryverify": "V",
-    "cvvverifycode": "V",
-    "paymentinstrumentid": "5212340000000005",
-    "customeracctnumber": "5212340000000005",
-    "transactioncategory": "M"
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
-   "时间窗口": "90天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000022_0128_G1_H004",
-    "biztime": "2026-07-27 14:30:00",
-    "policyCode": "Acq_Authorization",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-27",
-    "transactiontime": "14:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000022_0128_G1_H004",
-    "merchantid": "M001",
-    "merchantname": "MERCHANT_TEST",
-    "mcc": "5999",
-    "posentrymode": "C",
-    "transactionamount": 400,
-    "transactiontype": "M",
-    "terminalid": "T128",
-    "userindicator02": "D",
-    "authsecondaryverify": "V",
-    "cvvverifycode": "V",
-    "paymentinstrumentid": "5212340000000005",
-    "customeracctnumber": "5212340000000005",
-    "transactioncategory": "M"
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
-   "时间窗口": "90天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000022_0128_G1_H005",
-    "biztime": "2026-07-27 14:30:00",
-    "policyCode": "Acq_Authorization",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-27",
-    "transactiontime": "14:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000022_0128_G1_H005",
-    "merchantid": "M001",
-    "merchantname": "MERCHANT_TEST",
-    "mcc": "5999",
-    "posentrymode": "C",
-    "transactionamount": 400,
+    "transactionamount": 1000,
     "transactiontype": "M",
     "terminalid": "T128",
     "userindicator02": "D",
@@ -26458,17 +26347,17 @@
       </c>
       <c r="O126" s="38" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P126" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DMKG1QKIYRJFJVC</t>
+          <t>1785306600000115C267DA3ORUVZQM7UIVD</t>
         </is>
       </c>
       <c r="Q126" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件5需成立）；历史数据原卡在24h窗口边界（不在窗内），已移至当前笔前2小时 || 执行结果：规则未触发，正案例执行失败（命中规则: 无） 返回报文：126_ACQ_RS4_000022_正案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件5需成立）；历史数据原卡在24h窗口边界（不在窗内），已移至当前笔前2小时 || 执行结果：目标规则命中，符合预期 返回报文：126_ACQ_RS4_000022_正案例.json</t>
         </is>
       </c>
     </row>
@@ -27738,7 +27627,7 @@
     "merchantname": "MERCHANT_TEST",
     "mcc": "5999",
     "posentrymode": "C",
-    "transactionamount": 80000,
+    "transactionamount": 80500,
     "transactiontype": "M",
     "terminalid": "T136",
     "userindicator02": "D",
@@ -27785,7 +27674,7 @@
       </c>
       <c r="P132" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267D1J2SRALGWCXJHC</t>
+          <t>1785306600000115C267DJ2AW7T6HJOBGSK</t>
         </is>
       </c>
       <c r="Q132" s="38" t="inlineStr">
@@ -28123,7 +28012,8 @@
     "paymentinstrumentid": "5212340000000005",
     "customeracctnumber": "5212340000000005",
     "transactioncategory": "M"
-   }
+   },
+   "分散商户": 20
   },
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
@@ -28147,7 +28037,7 @@
     "merchantname": "MERCHANT_TEST",
     "mcc": "5411",
     "posentrymode": "C",
-    "transactionamount": 750,
+    "transactionamount": 2000,
     "transactiontype": "M",
     "terminalid": "T138",
     "userindicator02": "D",
@@ -28194,7 +28084,7 @@
       </c>
       <c r="P134" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DXP9W7ZQATHMX8A</t>
+          <t>1785306600000115C267DJDS0ULGOF5KFZZ</t>
         </is>
       </c>
       <c r="Q134" s="38" t="inlineStr">
@@ -28325,7 +28215,7 @@
     "merchantname": "MERCHANT_TEST",
     "mcc": "5411",
     "posentrymode": "C",
-    "transactionamount": 500,
+    "transactionamount": 2300,
     "transactiontype": "M",
     "terminalid": "T139",
     "userindicator02": "D",
@@ -28334,7 +28224,8 @@
     "paymentinstrumentid": "5212340000000005",
     "customeracctnumber": "5212340000000005",
     "transactioncategory": "M"
-   }
+   },
+   "分散商户": 20
   },
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
@@ -28358,7 +28249,7 @@
     "merchantname": "MERCHANT_TEST",
     "mcc": "5411",
     "posentrymode": "C",
-    "transactionamount": 687.5,
+    "transactionamount": 500,
     "transactiontype": "M",
     "terminalid": "T139",
     "userindicator02": "D",
@@ -28405,7 +28296,7 @@
       </c>
       <c r="P135" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DQPW916SV9J7FKS</t>
+          <t>1785306600000115C267DAV7AHS8UNZUS8P</t>
         </is>
       </c>
       <c r="Q135" s="38" t="inlineStr">
@@ -29331,12 +29222,12 @@
    "请求参数模板": {
     "apiModel": 20,
     "bizid": "BIZ_ACQ_RS4_000026_0144_G1_H{序号001-060}",
-    "biztime": "2026-07-28 14:30:00",
+    "biztime": "2026-07-14 14:30:00",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
+    "transactiondate": "2026-07-14",
     "transactiontime": "14:30:00",
     "externaltransactionid": "EXT_BIZ_ACQ_RS4_000026_0144_G1_H{序号001-060}",
     "merchantid": "M001",
@@ -29418,17 +29309,17 @@
       </c>
       <c r="O140" s="43" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P140" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DUK4CMB7QXFIKBF</t>
+          <t>1785306600000115C267DCRNVRP7S5PMGJF</t>
         </is>
       </c>
       <c r="Q140" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：规则未触发，正案例执行失败（命中规则: 无） 返回报文：140_ACQ_RS4_000026_正案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：目标规则命中，符合预期 返回报文：140_ACQ_RS4_000026_正案例.json</t>
         </is>
       </c>
     </row>
@@ -30349,13 +30240,13 @@
    "请求参数模板": {
     "apiModel": 20,
     "bizid": "BIZ_ACQ_RS4_000027_0149_G1_H{序号001-035}",
-    "biztime": "2026-07-28 14:30:00",
+    "biztime": "2026-07-28 04:00:00",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
     "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
+    "transactiontime": "04:00:00",
     "externaltransactionid": "EXT_BIZ_ACQ_RS4_000027_0149_G1_H{序号001-035}",
     "merchantid": "M001",
     "merchantname": "MERCHANT_TEST",
@@ -30376,13 +30267,13 @@
  "触发交易(当前笔)": {
   "apiModel": 20,
   "bizid": "BIZ_ACQ_RS4_000027_0149",
-  "biztime": "2026-07-29 14:30:00",
+  "biztime": "2026-07-29 03:00:00",
   "policyCode": "Acq_Authorization",
   "appCode": "Acquiring",
   "partnerCode": "kratos",
   "orgCode": "hlb_my",
   "transactiondate": "2026-07-29",
-  "transactiontime": "14:30:00",
+  "transactiontime": "03:00:00",
   "externaltransactionid": "EXT_BIZ_ACQ_RS4_000027_0149",
   "merchantid": "M001",
   "merchantname": "MERCHANT_TEST",
@@ -30403,17 +30294,17 @@
       </c>
       <c r="O145" s="37" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P145" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DZ6EOUJUD3DYNJ9</t>
+          <t>1785265200000115C267DBJCFMXLRVJLO3M</t>
         </is>
       </c>
       <c r="Q145" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：规则未触发，正案例执行失败（命中规则: 无） 返回报文：145_ACQ_RS4_000027_正案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：目标规则命中，符合预期 返回报文：145_ACQ_RS4_000027_正案例.json</t>
         </is>
       </c>
     </row>
@@ -31245,22 +31136,24 @@
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
    "时间窗口": "30天",
-   "请求参数": {
+   "批量生成数量": 20,
+   "分散天数": 20,
+   "请求参数模板": {
     "apiModel": 20,
     "bizid": "BIZ_ACQ_RS4_000028_0156_G1_H001",
-    "biztime": "2026-07-28 14:30:00",
+    "biztime": "2026-07-21 14:30:00",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
+    "transactiondate": "2026-07-21",
     "transactiontime": "14:30:00",
     "externaltransactionid": "EXT_BIZ_ACQ_RS4_000028_0156_G1_H001",
     "merchantid": "M001",
     "merchantname": "MERCHANT_TEST",
     "mcc": "5411",
     "posentrymode": "C",
-    "transactionamount": 100000,
+    "transactionamount": 5000,
     "transactiontype": "M",
     "terminalid": "T156",
     "userindicator02": "D",
@@ -31289,7 +31182,7 @@
     "merchantname": "MERCHANT_TEST",
     "mcc": "5411",
     "posentrymode": "C",
-    "transactionamount": 92000,
+    "transactionamount": 150000,
     "transactiontype": "M",
     "terminalid": "T156",
     "userindicator02": "D",
@@ -31332,17 +31225,17 @@
       </c>
       <c r="O150" s="37" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P150" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DJUOLUVUOFRZGOV</t>
+          <t>1785306600000115C267DQIS4W9M4GCZKB5</t>
         </is>
       </c>
       <c r="Q150" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260130（入网天数180天，条件4需成立） || 执行结果：规则未触发，正案例执行失败（命中规则: ACQ_RS4_000025） 返回报文：150_ACQ_RS4_000028_正案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260130（入网天数180天，条件4需成立） || 执行结果：目标规则命中，符合预期 返回报文：150_ACQ_RS4_000028_正案例.json</t>
         </is>
       </c>
     </row>
@@ -32072,9 +31965,12 @@
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
    "时间窗口": "近1天",
-   "请求参数": {
+   "批量生成数量": 6,
+   "分散商户": 3,
+   "字段分布说明": "同一客户账户号关联3个商户，6笔×6000=36000 MYR",
+   "请求参数模板": {
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000030_0163_G1_H001",
+    "bizid": "BIZ_ACQ_RS4_000030_0163_G1_H001_S{序号001-006}",
     "biztime": "2026-07-29 12:30:00",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
@@ -32082,12 +31978,12 @@
     "orgCode": "hlb_my",
     "transactiondate": "2026-07-29",
     "transactiontime": "12:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000030_0163_G1_H001",
+    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000030_0163_G1_H001_S{序号001-006}",
     "merchantid": "M001",
     "merchantname": "MERCHANT_TEST",
     "mcc": "5999",
     "posentrymode": "C",
-    "transactionamount": 35000,
+    "transactionamount": 6000,
     "transactiontype": "M",
     "terminalid": "T163",
     "userindicator02": "D",
@@ -32134,7 +32030,7 @@
       </c>
       <c r="P154" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DSKRF4HK5NG9VSO</t>
+          <t>1785306600000115C267DDT9Q0N38FVDG1P</t>
         </is>
       </c>
       <c r="Q154" s="38" t="inlineStr">
@@ -35478,7 +35374,8 @@
     "paymentinstrumentid": "5212340000000005",
     "customeracctnumber": "5212340000000005",
     "transactioncategory": "M"
-   }
+   },
+   "分散商户": 20
   },
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
@@ -35507,7 +35404,8 @@
     "paymentinstrumentid": "5212340000000005",
     "customeracctnumber": "5212340000000005",
     "transactioncategory": "M"
-   }
+   },
+   "分散商户": 20
   }
  ],
  "触发交易(当前笔)": {
@@ -35540,17 +35438,17 @@
       </c>
       <c r="O171" s="44" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P171" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DOETTF8V06BVBSL</t>
+          <t>1785306600000115C267DMHWYPX6UM6IYHQ</t>
         </is>
       </c>
       <c r="Q171" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：规则未触发，正案例执行失败（命中规则: ACQ_RS4_000025） 返回报文：171_ACQ_RS4_000035_正案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：目标规则命中，符合预期 返回报文：171_ACQ_RS4_000035_正案例.json</t>
         </is>
       </c>
     </row>

--- a/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
+++ b/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
@@ -24661,17 +24661,17 @@
       </c>
       <c r="O118" s="38" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P118" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DAWEQA486TD3LV8</t>
+          <t>1785306600000115C267DPYQAIXEBPR7WZR</t>
         </is>
       </c>
       <c r="Q118" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件3需成立）；历史数据原卡在24h窗口边界（不在窗内），已移至当前笔前2小时 || 执行结果：规则触发，反案例执行失败（命中规则: ACQ_RS4_000020） 返回报文：118_ACQ_RS4_000020_反案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件3需成立）；历史数据原卡在24h窗口边界（不在窗内），已移至当前笔前2小时 || 执行结果：目标规则未命中，符合预期 返回报文：118_ACQ_RS4_000020_反案例.json</t>
         </is>
       </c>
     </row>
@@ -26135,17 +26135,17 @@
       </c>
       <c r="O125" s="43" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P125" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DRVBRORABCKQVRZ</t>
+          <t>1785306600000115C267DCTETILIAQGOSLW</t>
         </is>
       </c>
       <c r="Q125" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件5需成立）；历史数据原卡在24h窗口边界（不在窗内），已移至当前笔前2小时 || 执行结果：规则未触发，正案例执行失败（命中规则: ACQ_RS4_000020,ACQ_RS4_000025） 返回报文：125_ACQ_RS4_000022_正案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件5需成立）；历史数据原卡在24h窗口边界（不在窗内），已移至当前笔前2小时 || 执行结果：目标规则命中，符合预期 返回报文：125_ACQ_RS4_000022_正案例.json</t>
         </is>
       </c>
     </row>
@@ -27273,17 +27273,17 @@
       </c>
       <c r="O130" s="38" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P130" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DY0SKP0BRF4GNZX</t>
+          <t>1785306600000115C267DSP9JMNMBC200JP</t>
         </is>
       </c>
       <c r="Q130" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；历史数据原卡在24h窗口边界（不在窗内），已移至当前笔前2小时 || 执行结果：规则触发，反案例执行失败（命中规则: ACQ_RS4_000023） 返回报文：130_ACQ_RS4_000023_反案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；历史数据原卡在24h窗口边界（不在窗内），已移至当前笔前2小时 || 执行结果：目标规则未命中，符合预期 返回报文：130_ACQ_RS4_000023_反案例.json</t>
         </is>
       </c>
     </row>
@@ -27674,7 +27674,7 @@
       </c>
       <c r="P132" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DJ2AW7T6HJOBGSK</t>
+          <t>1785306600000115C267DHOCKNAA0MPNK7R</t>
         </is>
       </c>
       <c r="Q132" s="38" t="inlineStr">
@@ -29008,14 +29008,13 @@
  "历史数据(构造事件历史)": [
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
-   "批量生成数量": 500,
-   "时间窗口": "规则指定时间窗口",
-   "bizid规则": "BIZ_ACQ_RS4_000025_0143_G1_H001~H500",
-   "字段分布说明": "阈值/要求=≥500笔 ✗（不满足）",
-   "字段分布": [],
+   "时间窗口": "近30天",
+   "批量生成数量": 418,
+   "分散商户": 20,
+   "字段分布说明": "同MCC其他商户基准418笔×200（MCC总笔数=499&lt;500，破坏C5）",
    "请求参数模板": {
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000025_0143_G1_H{序号001-500}",
+    "bizid": "BIZ_ACQ_RS4_000025_0143_G1_H{序号001-500}_B{序号001-418}",
     "biztime": "2026-07-29 14:29:00",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
@@ -29023,12 +29022,12 @@
     "orgCode": "hlb_my",
     "transactiondate": "2026-07-29",
     "transactiontime": "14:29:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000025_0143_G1_H{序号001-500}",
+    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000025_0143_G1_H{序号001-500}_B{序号001-418}",
     "merchantid": "M143",
     "merchantname": "MERCHANT_TEST",
     "mcc": "5999",
     "posentrymode": "C",
-    "transactionamount": 300,
+    "transactionamount": 200,
     "transactiontype": "M",
     "terminalid": "T143",
     "userindicator02": "D",
@@ -29041,10 +29040,12 @@
   },
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
-   "时间窗口": "规则指定时间窗口",
-   "请求参数": {
+   "时间窗口": "近30天",
+   "批量生成数量": 80,
+   "字段分布说明": "目标商户80笔×1500（均值1485≥3×MCC均值408，C1成立）",
+   "请求参数模板": {
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000025_0143_G2_H001",
+    "bizid": "BIZ_ACQ_RS4_000025_0143_G1_H{序号001-500}_T{序号001-080}",
     "biztime": "2026-07-29 14:29:00",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
@@ -29052,12 +29053,12 @@
     "orgCode": "hlb_my",
     "transactiondate": "2026-07-29",
     "transactiontime": "14:29:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000025_0143_G2_H001",
+    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000025_0143_G1_H{序号001-500}_T{序号001-080}",
     "merchantid": "M143",
     "merchantname": "MERCHANT_TEST",
     "mcc": "5999",
     "posentrymode": "C",
-    "transactionamount": 500,
+    "transactionamount": 1500,
     "transactiontype": "M",
     "terminalid": "T143",
     "userindicator02": "D",
@@ -29099,17 +29100,17 @@
       </c>
       <c r="O139" s="38" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P139" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267D1J0LLHGKAL3YM5</t>
+          <t>1785306600000115C267DRPRSIALBZIQJIA</t>
         </is>
       </c>
       <c r="Q139" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：规则触发，反案例执行失败（命中规则: ACQ_RS4_000025） 返回报文：139_ACQ_RS4_000025_反案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：目标规则未命中，符合预期 返回报文：139_ACQ_RS4_000025_反案例.json</t>
         </is>
       </c>
     </row>
@@ -32030,7 +32031,7 @@
       </c>
       <c r="P154" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DDT9Q0N38FVDG1P</t>
+          <t>1785306600000115C267D1I9YTZSWKQF6MN</t>
         </is>
       </c>
       <c r="Q154" s="38" t="inlineStr">

--- a/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
+++ b/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
@@ -24946,16 +24946,16 @@
    "请求参数模板": {
     "apiModel": 20,
     "bizid": "BIZ_ACQ_RS4_000020_0122_G1_H{序号001-051}",
-    "biztime": "2026-07-27 14:30:00",
+    "biztime": "2026-07-29 12:30:00",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-27",
-    "transactiontime": "14:30:00",
+    "transactiondate": "2026-07-29",
+    "transactiontime": "12:30:00",
     "externaltransactionid": "EXT_BIZ_ACQ_RS4_000020_0122_G1_H{序号001-051}",
     "merchantid": "M122",
-    "merchantname": "MERCHANT_TEST",
+    "merchantname": "KEY_MERCHANT_001",
     "mcc": "5999",
     "posentrymode": "C",
     "transactionamount": 20001,
@@ -24982,7 +24982,7 @@
   "transactiontime": "14:30:00",
   "externaltransactionid": "EXT_BIZ_ACQ_RS4_000020_0122",
   "merchantid": "M122",
-  "merchantname": "MERCHANT_TEST",
+  "merchantname": "KEY_MERCHANT_001",
   "mcc": "5999",
   "posentrymode": "C",
   "transactionamount": 20001,
@@ -25006,12 +25006,12 @@
       </c>
       <c r="P120" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DNZZPGZDKPTXMAZ</t>
+          <t>1785306600000115C267DGHH2UZ1QKYS0QO</t>
         </is>
       </c>
       <c r="Q120" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件3需成立） || 执行结果：规则触发，反案例执行失败（命中规则: ACQ_RS4_000020,ACQ_RS4_000025） 返回报文：120_ACQ_RS4_000020_反案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件3需成立） || 执行结果：规则触发，反案例执行失败（命中规则: ACQ_RS4_000020,ACQ_RS4_000022,ACQ_RS4_000023,ACQ_RS4_000025） 返回报文：120_ACQ_RS4_000020_反案例.json</t>
         </is>
       </c>
     </row>
@@ -28020,7 +28020,7 @@
    "批量生成数量": 80,
    "时间窗口": "30天",
    "bizid规则": "BIZ_ACQ_RS4_000025_0138_G2_H001~H080",
-   "字段分布说明": "2. 商户M001(MCC=5411)30天: 笔数80，总金额60000 MYR，均值=750 MYR",
+   "字段分布说明": "2. 目标商户30天: 80笔×3000，均值2967（按平台threshold_3x指标≈2241反推）",
    "字段分布": [],
    "请求参数模板": {
     "apiModel": 20,
@@ -28037,7 +28037,7 @@
     "merchantname": "MERCHANT_TEST",
     "mcc": "5411",
     "posentrymode": "C",
-    "transactionamount": 2000,
+    "transactionamount": 3000,
     "transactiontype": "M",
     "terminalid": "T138",
     "userindicator02": "D",
@@ -28079,17 +28079,17 @@
       </c>
       <c r="O134" s="37" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P134" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DJDS0ULGOF5KFZZ</t>
+          <t>1785306600000115C267DS8EX1SNZYOPP0G</t>
         </is>
       </c>
       <c r="Q134" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：规则未触发，正案例执行失败（命中规则: 无） 返回报文：134_ACQ_RS4_000025_正案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：目标规则命中，符合预期 返回报文：134_ACQ_RS4_000025_正案例.json</t>
         </is>
       </c>
     </row>
@@ -28229,10 +28229,10 @@
   },
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
-   "批量生成数量": 80,
+   "批量生成数量": 300,
    "时间窗口": "30天",
    "bizid规则": "BIZ_ACQ_RS4_000025_0139_G2_H001~H080",
-   "字段分布说明": "2. 商户M002(MCC=5411)30天: 笔数80，总金额55000 MYR，均值=100 MYR",
+   "字段分布说明": "2. 目标商户30天: 300笔×170，均值170.4（≤平台threshold_30pct指标≈220），笔数301≥50，金额51300≥50000",
    "字段分布": [],
    "请求参数模板": {
     "apiModel": 20,
@@ -28249,7 +28249,7 @@
     "merchantname": "MERCHANT_TEST",
     "mcc": "5411",
     "posentrymode": "C",
-    "transactionamount": 500,
+    "transactionamount": 170,
     "transactiontype": "M",
     "terminalid": "T139",
     "userindicator02": "D",
@@ -28291,17 +28291,17 @@
       </c>
       <c r="O135" s="38" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P135" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DAV7AHS8UNZUS8P</t>
+          <t>1785306600000115C267DAQGPN9LNQGEM42</t>
         </is>
       </c>
       <c r="Q135" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：规则未触发，正案例执行失败（命中规则: 无） 返回报文：135_ACQ_RS4_000025_正案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源） || 执行结果：目标规则命中，符合预期 返回报文：135_ACQ_RS4_000025_正案例.json</t>
         </is>
       </c>
     </row>
@@ -31966,12 +31966,13 @@
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
    "时间窗口": "近1天",
-   "批量生成数量": 6,
-   "分散商户": 3,
-   "字段分布说明": "同一客户账户号关联3个商户，6笔×6000=36000 MYR",
+   "批量生成数量": 102,
+   "分散商户": 2,
+   "商户起始": 1,
+   "字段分布说明": "商户A/B各51笔×500=25500（各自满足000020: 笔数&gt;50且金额&gt;20000且入网30天，构造短期交易激增标签）",
    "请求参数模板": {
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000030_0163_G1_H001_S{序号001-006}",
+    "bizid": "BIZ_ACQ_RS4_000030_S_A{序号001-102}",
     "biztime": "2026-07-29 12:30:00",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
@@ -31979,12 +31980,12 @@
     "orgCode": "hlb_my",
     "transactiondate": "2026-07-29",
     "transactiontime": "12:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000030_0163_G1_H001_S{序号001-006}",
+    "externaltransactionid": "EXT_ACQ_RS4_000030_S_A{序号001-102}",
     "merchantid": "M001",
     "merchantname": "MERCHANT_TEST",
     "mcc": "5999",
     "posentrymode": "C",
-    "transactionamount": 6000,
+    "transactionamount": 500,
     "transactiontype": "M",
     "terminalid": "T163",
     "userindicator02": "D",
@@ -31992,7 +31993,42 @@
     "cvvverifycode": "V",
     "paymentinstrumentid": "5212340000000005",
     "customeracctnumber": "5212340000000005",
-    "transactioncategory": "M"
+    "transactioncategory": "M",
+    "aisopendate": "20260629"
+   }
+  },
+  {
+   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
+   "时间窗口": "近1天",
+   "批量生成数量": 1,
+   "分散商户": 1,
+   "商户起始": 3,
+   "字段分布说明": "商户C 1笔×5000（凑齐关联商户≥3）",
+   "请求参数模板": {
+    "apiModel": 20,
+    "bizid": "BIZ_ACQ_RS4_000030_S_B001",
+    "biztime": "2026-07-29 12:30:00",
+    "policyCode": "Acq_Authorization",
+    "appCode": "Acquiring",
+    "partnerCode": "kratos",
+    "orgCode": "hlb_my",
+    "transactiondate": "2026-07-29",
+    "transactiontime": "12:30:00",
+    "externaltransactionid": "EXT_ACQ_RS4_000030_S_B001",
+    "merchantid": "M001",
+    "merchantname": "MERCHANT_TEST",
+    "mcc": "5999",
+    "posentrymode": "C",
+    "transactionamount": 5000,
+    "transactiontype": "M",
+    "terminalid": "T163",
+    "userindicator02": "D",
+    "authsecondaryverify": "V",
+    "cvvverifycode": "V",
+    "paymentinstrumentid": "5212340000000005",
+    "customeracctnumber": "5212340000000005",
+    "transactioncategory": "M",
+    "aisopendate": "20260629"
    }
   }
  ],
@@ -32019,7 +32055,8 @@
   "cvvverifycode": "V",
   "paymentinstrumentid": "5212340000000005",
   "customeracctnumber": "5212340000000005",
-  "transactioncategory": "M"
+  "transactioncategory": "M",
+  "aisopendate": "20260629"
  }
 }</t>
         </is>
@@ -32031,7 +32068,7 @@
       </c>
       <c r="P154" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267D1I9YTZSWKQF6MN</t>
+          <t>1785306600000115C267DIT0TWEU567TSKM</t>
         </is>
       </c>
       <c r="Q154" s="38" t="inlineStr">

--- a/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
+++ b/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
@@ -4572,14 +4572,16 @@
       </c>
       <c r="L18" s="38" t="inlineStr">
         <is>
-          <t>步骤1：准备1个非VIP普通商户M1
+          <t>步骤1：准备1个非VIP普通商户M1（merchantId=M1，AisVipType≠V，不在ACQ_KEYMIDS名单内）
 步骤2：构造历史交易满足条件1、2（近2天有磁条+近1天磁条占比&gt;1%）
-步骤3：当前笔交易posEntryMode=C（芯片卡，不在磁条列表中）
+步骤3：验证各条件指标：
   ★ 预期失败条件：条件3（当前笔POS录入方式）
-  - 条件1-2：全部 ✓
-  - 条件3：当前笔posEntryMode=C ∉ {F,G,S,U} ✗
-  - 条件4-5：全部 ✓
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+  - 条件1：近2天磁条销售交易天数（含当前笔）= 2 ≥ 2 ✓
+  - 条件2：近1天磁条销售笔数 &gt; 总笔数×1% ✓
+  - 条件3：当前笔posEntryMode = C ∉ {F,G,S,U} ✗
+  - 条件4：当前笔AisVipType ≠ V ✓
+  - 条件5：当前笔merchantId ∉ ACQ_KEYMIDS ✓
+步骤4：提交当前交易（posEntryMode=C，merchantId=M1），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M18" s="38" t="inlineStr">
@@ -4804,14 +4806,16 @@
       </c>
       <c r="L19" s="38" t="inlineStr">
         <is>
-          <t>步骤1：准备1个VIP商户M1（AisVipType=V）
+          <t>步骤1：准备1个VIP商户M1（merchantId=M1，AisVipType=V，不在ACQ_KEYMIDS名单内）
 步骤2：构造历史交易满足条件1-3、5
-步骤3：当前笔交易AisVipType=V
+步骤3：验证各条件指标：
   ★ 预期失败条件：条件4（是否VIP）
-  - 条件1-3：全部 ✓
-  - 条件4：AisVipType = V（不应≠V）✗
-  - 条件5：全部 ✓
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+  - 条件1：近2天磁条销售交易天数（含当前笔）= 2 ≥ 2 ✓
+  - 条件2：近1天磁条销售笔数 &gt; 总笔数×1% ✓
+  - 条件3：当前笔posEntryMode = F ∈ {F,G,S,U} ✓
+  - 条件4：当前笔AisVipType = V（不等于≠V）✗
+  - 条件5：当前笔merchantId ∉ ACQ_KEYMIDS ✓
+步骤4：提交当前交易（posEntryMode=F，AisVipType=V，merchantId=M1），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M19" s="38" t="inlineStr">
@@ -5091,13 +5095,16 @@
       </c>
       <c r="L20" s="38" t="inlineStr">
         <is>
-          <t>步骤1：准备1个重点商户M_KEY（在ACQ_KEYMIDS名单内）
+          <t>步骤1：准备1个重点商户M_KEY（merchantId=M_KEY ∈ ACQ_KEYMIDS，AisVipType≠V）
 步骤2：构造历史交易满足条件1-4
-步骤3：当前笔交易merchantId=M_KEY ∈ ACQ_KEYMIDS
+步骤3：验证各条件指标：
   ★ 预期失败条件：条件5（商户不在名单内）
-  - 条件1-4：全部 ✓
-  - 条件5：merchantId ∈ ACQ_KEYMIDS ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+  - 条件1：近2天磁条销售交易天数（含当前笔）= 2 ≥ 2 ✓
+  - 条件2：近1天磁条销售笔数 &gt; 总笔数×1% ✓
+  - 条件3：当前笔posEntryMode = F ∈ {F,G,S,U} ✓
+  - 条件4：当前笔AisVipType ≠ V ✓
+  - 条件5：当前笔merchantId = M_KEY ∈ ACQ_KEYMIDS ✗
+步骤4：提交当前交易（posEntryMode=F，merchantId=M_KEY），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M20" s="38" t="inlineStr">
@@ -5670,12 +5677,16 @@
       </c>
       <c r="L22" s="38" t="inlineStr">
         <is>
-          <t>步骤1：准备1个非VIP普通商户M1
-步骤2：仅在近1天内有手工录入(posEntryMode=K)销售交易（仅1天）
-步骤3：★ 预期失败条件：条件1
-  - 条件1：近2天手工录入销售交易天数=1 &lt; 2 ✗
-  - 条件2-5：全部 ✓
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+          <t>步骤1：准备1个非VIP普通商户M1（不在ACQ_KEYMIDS名单内）
+步骤2：仅在近1天内有手工录入(posEntryMode=K)销售交易（仅1天，不满足2天要求）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（手工录入交易天数）
+  - 条件1：近2天手工录入销售交易天数（含当前笔）= 1 &lt; 2 ✗
+  - 条件2：近1天手工录入笔数 &gt; 总笔数×1% ✓
+  - 条件3：当前笔posEntryMode = K ✓
+  - 条件4：当前笔AisVipType ≠ V ✓
+  - 条件5：当前笔merchantId ∉ ACQ_KEYMIDS ✓
+步骤4：提交当前交易（posEntryMode=K，merchantId=M1），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M22" s="38" t="inlineStr">
@@ -6068,12 +6079,16 @@
       </c>
       <c r="L24" s="38" t="inlineStr">
         <is>
-          <t>步骤1：准备1个非VIP普通商户M1
+          <t>步骤1：准备1个非VIP普通商户M1（不在ACQ_KEYMIDS名单内）
 步骤2：构造历史交易满足条件1、2
-步骤3：当前笔posEntryMode=C（芯片卡，不是K）
-  ★ 预期失败条件：条件3
-  - 条件3：posEntryMode=C ≠ K ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（当前笔POS录入方式）
+  - 条件1：近2天手工录入销售交易天数（含当前笔）= 2 ≥ 2 ✓
+  - 条件2：近1天手工录入笔数 &gt; 总笔数×1% ✓
+  - 条件3：当前笔posEntryMode = C ≠ K ✗
+  - 条件4：当前笔AisVipType ≠ V ✓
+  - 条件5：当前笔merchantId ∉ ACQ_KEYMIDS ✓
+步骤4：提交当前交易（posEntryMode=C，merchantId=M1），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M24" s="38" t="inlineStr">
@@ -6298,10 +6313,16 @@
       </c>
       <c r="L25" s="38" t="inlineStr">
         <is>
-          <t>步骤1：准备1个VIP商户（AisVipType=V）
+          <t>步骤1：准备1个VIP商户M1（AisVipType=V）
 步骤2：构造历史交易满足条件1-3、5
-步骤3：★ 预期失败条件：条件4，AisVipType = V ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（是否VIP）
+  - 条件1：近2天手工录入销售交易天数（含当前笔）= 2 ≥ 2 ✓
+  - 条件2：近1天手工录入笔数 &gt; 总笔数×1% ✓
+  - 条件3：当前笔posEntryMode = K ✓
+  - 条件4：当前笔AisVipType = V（不等于≠V）✗
+  - 条件5：当前笔merchantId ∉ ACQ_KEYMIDS ✓
+步骤4：提交当前交易（posEntryMode=K，AisVipType=V），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M25" s="38" t="inlineStr">
@@ -6581,10 +6602,16 @@
       </c>
       <c r="L26" s="38" t="inlineStr">
         <is>
-          <t>步骤1：准备1个重点商户M_KEY
+          <t>步骤1：准备1个重点商户M_KEY（merchantId ∈ ACQ_KEYMIDS）
 步骤2：构造历史交易满足条件1-4
-步骤3：★ 预期失败条件：条件5，merchantId ∈ ACQ_KEYMIDS ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件5（商户不在名单内）
+  - 条件1：近2天手工录入销售交易天数（含当前笔）= 2 ≥ 2 ✓
+  - 条件2：近1天手工录入笔数 &gt; 总笔数×1% ✓
+  - 条件3：当前笔posEntryMode = K ✓
+  - 条件4：当前笔AisVipType ≠ V ✓
+  - 条件5：当前笔merchantId = M_KEY ∈ ACQ_KEYMIDS ✗
+步骤4：提交当前交易（posEntryMode=K，merchantId=M_KEY），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M26" s="38" t="inlineStr">
@@ -7059,11 +7086,16 @@
       <c r="L28" s="38" t="inlineStr">
         <is>
           <t>步骤1：准备1个商户M1
-步骤2：近24小时构造30笔线上大额(≥250)销售交易，其中9笔authSecondaryVerify≠V，21笔=V
-步骤3：★ 预期失败条件：条件1
-  - 条件1：无3DS笔数(9) &gt; 30×0.3=9？9 &gt; 9 不成立 ✗
-  - 条件2-5：全部 ✓
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤2：近24小时构造30笔线上大额(≥250)销售交易，其中仅9笔authSecondaryVerify≠V（无3DS），21笔=V（有3DS）
+  （无3DS笔数9 ≤ 30×0.3=9，不满足 &gt;9 的条件）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（无3DS大额线上笔数占比&gt;30%）
+  - 条件1：无3DS大额线上笔数(9) &gt; 30×0.3=9？9 &gt; 9 不成立 ✗
+  - 条件2：近24小时大额线上累计笔数(30) ≥ 30 ✓
+  - 条件3：当前笔posEntryMode = E ✓
+  - 条件4：当前笔authSecondaryVerify ≠ V ✓
+  - 条件5：当前笔交易金额(≥250) ≥ 250 ✓
+步骤4：提交当前交易（posEntryMode=E，amount=250，authSecondaryVerify=N），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M28" s="38" t="inlineStr">
@@ -7244,10 +7276,15 @@
       <c r="L29" s="38" t="inlineStr">
         <is>
           <t>步骤1：准备1个商户M1
-步骤2：近24小时构造29笔线上大额销售交易
-步骤3：★ 预期失败条件：条件2
-  - 条件2：大额线上总笔数(29) &lt; 30 ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤2：近24小时构造29笔线上大额(≥250)销售交易（不满足30笔门槛）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（大额线上累计笔数≥30）
+  - 条件1：无3DS大额线上笔数 &gt; 总笔数×30% ✓
+  - 条件2：近24小时大额线上累计笔数(29) &lt; 30 ✗
+  - 条件3：当前笔posEntryMode = E ✓
+  - 条件4：当前笔authSecondaryVerify ≠ V ✓
+  - 条件5：当前笔交易金额(≥250) ≥ 250 ✓
+步骤4：提交当前交易（posEntryMode=E，amount=250），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M29" s="38" t="inlineStr">
@@ -7428,11 +7465,15 @@
       <c r="L30" s="38" t="inlineStr">
         <is>
           <t>步骤1：准备1个商户M1
-步骤2：构造历史交易满足条件1、2
-步骤3：当前笔posEntryMode=F（磁条，不是E）
-  ★ 预期失败条件：条件3
-  - 条件3：posEntryMode=F ≠ E ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤2：构造历史交易满足条件1、2（总笔数≥30 + 无3DS占比&gt;30%）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（当前笔POS录入方式）
+  - 条件1：无3DS大额线上笔数 &gt; 总笔数×30% ✓
+  - 条件2：近24小时大额线上累计笔数 ≥ 30 ✓
+  - 条件3：当前笔posEntryMode = F ≠ E ✗
+  - 条件4：当前笔authSecondaryVerify ≠ V ✓
+  - 条件5：当前笔交易金额(≥250) ≥ 250 ✓
+步骤4：提交当前交易（posEntryMode=F，amount=250），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M30" s="38" t="inlineStr">
@@ -7614,10 +7655,14 @@
         <is>
           <t>步骤1：准备1个商户M1
 步骤2：构造历史交易满足条件1-3、5
-步骤3：当前笔authSecondaryVerify=V
-  ★ 预期失败条件：条件4
-  - 条件4：authSecondaryVerify = V（不等于≠V）✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（当前笔有3DS验证）
+  - 条件1：无3DS大额线上笔数 &gt; 总笔数×30% ✓
+  - 条件2：近24小时大额线上累计笔数 ≥ 30 ✓
+  - 条件3：当前笔posEntryMode = E ✓
+  - 条件4：当前笔authSecondaryVerify = V（不等于≠V）✗
+  - 条件5：当前笔交易金额(≥250) ≥ 250 ✓
+步骤4：提交当前交易（posEntryMode=E，amount=250，authSecondaryVerify=V），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M31" s="38" t="inlineStr">
@@ -7799,10 +7844,14 @@
         <is>
           <t>步骤1：准备1个商户M1
 步骤2：构造历史交易满足条件1-4
-步骤3：当前笔交易金额=249（&lt;250）
-  ★ 预期失败条件：条件5
-  - 条件5：交易金额(249) &lt; 250 ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件5（当前笔金额≥250）
+  - 条件1：无3DS大额线上笔数 &gt; 总笔数×30% ✓
+  - 条件2：近24小时大额线上累计笔数 ≥ 30 ✓
+  - 条件3：当前笔posEntryMode = E ✓
+  - 条件4：当前笔authSecondaryVerify ≠ V ✓
+  - 条件5：当前笔交易金额(249) &lt; 250 ✗
+步骤4：提交当前交易（posEntryMode=E，amount=249），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M32" s="38" t="inlineStr">
@@ -8611,10 +8660,12 @@
       <c r="L36" s="38" t="inlineStr">
         <is>
           <t>步骤1：准备1个终端T1
-步骤2：构造近24小时仅有49笔销售交易
-步骤3：★ 预期失败条件：条件1
+步骤2：构造近24小时仅有49笔销售交易（不满足50笔门槛）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（总销售笔数≥50）
   - 条件1：总销售笔数(49) &lt; 50 ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+  - 条件2-5：不满足入门门槛，不再验证
+步骤4：提交当前交易（posEntryMode=F），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M36" s="38" t="inlineStr">
@@ -8795,11 +8846,13 @@
       <c r="L37" s="38" t="inlineStr">
         <is>
           <t>步骤1：准备1个终端T1
-步骤2：构造历史交易满足条件1和条件2
-步骤3：当前笔posEntryMode=C（芯片卡，不在{F,G}中）
-  ★ 预期失败条件：条件5
-  - 条件5：posEntryMode=C ∉ {F,G} ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤2：构造历史交易满足条件1和条件2（总笔数≥50 + 降级占比≥10%，走C2分支）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件5（当前笔POS录入方式）
+  - 条件1：总销售笔数 ≥ 50 ✓
+  - 条件2：降级笔数 ≥ 总笔数×10% ✓ → 走C2分支
+  - 条件5：当前笔posEntryMode = C ∉ {F,G} ✗
+步骤4：提交当前交易（posEntryMode=C），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M37" s="38" t="inlineStr">
@@ -8981,13 +9034,14 @@
         <is>
           <t>步骤1：准备1个终端T1
 步骤2：构造近24小时60笔正常芯片(posEntryMode=C)销售交易，无降级、无验证异常、无拒绝
-步骤3：★ 预期失败条件：条件2、3、4均不满足
-  - 条件1：总笔数(60) ≥ 50 ✓
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2、3、4均不满足
+  - 条件1：总销售笔数(60) ≥ 50 ✓
   - 条件2：降级笔数(0) &lt; 60×0.1=6 ✗
   - 条件3：验证异常银行卡数(0) &lt; 5 ✗
   - 条件4：拒绝笔数(0) &lt; 60×0.2=12 ✗
-  - 条件5：当前笔posEntryMode=F ✓
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+  - 条件5：当前笔posEntryMode = F ✓（但C2/C3/C4均不成立）
+步骤4：提交当前交易（posEntryMode=F），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M38" s="38" t="inlineStr">
@@ -9565,10 +9619,13 @@
       </c>
       <c r="L41" s="38" t="inlineStr">
         <is>
-          <t>步骤1：准备1个终端T1
-步骤2：构造近5分钟20笔线下销售交易，但仅9张不同银行卡
-步骤3：★ 预期失败条件：条件2
-  - 条件2：银行卡数(9) &lt; 10 ✗
+          <t>步骤1：准备1个终端T1，商户MCC=5812（非油站）
+步骤2：构造近5分钟20笔线下销售交易，但仅9张不同银行卡（不满足10张要求）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（银行卡数≥10）
+  - 条件1：近5分钟销售笔数(20) ≥ 20 ✓
+  - 条件2：近5分钟银行卡数(9) &lt; 10 ✗
+  - 条件3-5：不满足条件2，不再验证
 步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
@@ -9907,12 +9964,16 @@
       </c>
       <c r="L43" s="38" t="inlineStr">
         <is>
-          <t>步骤1：准备1个终端T1
+          <t>步骤1：准备1个终端T1，商户MCC=5812（非油站）
 步骤2：构造历史交易满足条件1-3、5
-步骤3：当前笔posEntryMode=E（线上，不在线下列表中）
-  ★ 预期失败条件：条件4
-  - 条件4：posEntryMode=E ∉ {C,D,F,G,S,T,U,V} ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（当前笔POS录入方式在线下列表中）
+  - 条件1：近5分钟销售笔数 ≥ 20 ✓
+  - 条件2：近5分钟银行卡数 ≥ 10 ✓
+  - 条件3：近5分钟交易金额 ≥ 3000 ✓
+  - 条件4：当前笔posEntryMode = E ∉ {C,D,F,G,S,T,U,V} ✗
+  - 条件5：当前笔MCC=5812 ∉ {5542,5541} ✓
+步骤4：提交当前交易（posEntryMode=E），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M43" s="38" t="inlineStr">
@@ -10081,9 +10142,14 @@
         <is>
           <t>步骤1：准备1个终端T1，商户MCC=5542（油站）
 步骤2：构造历史交易满足条件1-4
-步骤3：★ 预期失败条件：条件5
-  - 条件5：MCC=5542 ∈ {5542,5541} ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件5（MCC不在油站排除列表）
+  - 条件1：近5分钟销售笔数 ≥ 20 ✓
+  - 条件2：近5分钟银行卡数 ≥ 10 ✓
+  - 条件3：近5分钟交易金额 ≥ 3000 ✓
+  - 条件4：当前笔posEntryMode在线下列表中 ✓
+  - 条件5：当前笔MCC=5542 ∈ {5542,5541} ✗
+步骤4：提交当前交易（MCC=5542），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M44" s="38" t="inlineStr">
@@ -10603,9 +10669,13 @@
       </c>
       <c r="L47" s="38" t="inlineStr">
         <is>
-          <t>步骤1：准备1个商户M1
-步骤2：构造近10分钟15笔线下销售交易，仅4张不同银行卡
-步骤3：★ 预期失败条件：条件2，银行卡数(4) &lt; 5 ✗
+          <t>步骤1：准备1个商户M1，MCC=5999（不在白名单内）
+步骤2：构造近10分钟15笔线下销售交易，仅4张不同银行卡（不满足5张要求）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（银行卡数≥5）
+  - 条件1：近10分钟线下销售笔数(15) ≥ 15 ✓
+  - 条件2：近10分钟银行卡数(4) &lt; 5 ✗
+  - 条件3-5：不满足条件2，不再验证
 步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
@@ -10943,10 +11013,16 @@
       </c>
       <c r="L49" s="38" t="inlineStr">
         <is>
-          <t>步骤1：准备1个商户M1，MCC=5542
+          <t>步骤1：准备1个商户M1，MCC=5542（油站，在白名单内）
 步骤2：构造历史交易满足条件1-4
-步骤3：★ 预期失败条件：条件5，MCC=5542 ∈ 白名单 ✗
-步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件5（MCC不在白名单）
+  - 条件1：近10分钟线下销售笔数 ≥ 15 ✓
+  - 条件2：近10分钟银行卡数 ≥ 5 ✓
+  - 条件3：近10分钟交易金额 ≥ 3000 ✓
+  - 条件4：当前笔posEntryMode在线下列表中 ✓
+  - 条件5：当前笔MCC=5542 ∈ 白名单 ✗
+步骤4：提交当前交易（MCC=5542），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M49" s="38" t="inlineStr">
@@ -11392,9 +11468,13 @@
       </c>
       <c r="L51" s="38" t="inlineStr">
         <is>
-          <t>步骤1：构造近30天境外卡占比=30%&gt;20%
-步骤2：★ 预期失败条件：条件1，境外卡占比(30%) &gt; 20% ✗
-步骤3：提交当前交易，进入事件历史模块验证预期结果</t>
+          <t>步骤1：准备1个商户M1，MCC=5999（不在排除列表）
+步骤2：构造近30天境外卡占比=30%&gt;20%（不满足≤20%条件）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（近30天境外卡占比≤20%）
+  - 条件1：近30天境外卡占比(30%) &gt; 20% ✗
+  - 条件2-7：不满足条件1，不再验证
+步骤4：提交当前交易（cardborder=I），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M51" s="38" t="inlineStr">
@@ -12063,9 +12143,18 @@
       </c>
       <c r="L54" s="38" t="inlineStr">
         <is>
-          <t>步骤1：构造近2h境外卡金额=19999&lt;20000
-步骤2：★ 预期失败条件：条件5 ✗
-步骤3：提交当前交易，进入事件历史模块验证预期结果</t>
+          <t>步骤1：准备1个商户M1，MCC=5999（不在排除列表）
+步骤2：构造近30天满足条件1-2；近2h满足条件3-4，但境外卡金额=19999&lt;20000
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件5（近2h境外卡金额≥20000）
+  - 条件1：近30天境外卡占比 ≤ 20% ✓
+  - 条件2：近30天总销售金额 ≥ 50000 ✓
+  - 条件3：近2h境外卡金额占总金额 ≥ 70% ✓
+  - 条件4：近2h境外卡笔数 ≥ 5 ✓
+  - 条件5：近2h境外卡金额(19999) &lt; 20000 ✗
+  - 条件6：当前笔cardborder = I ✓
+  - 条件7：当前笔MCC ∉ 排除列表 ✓
+步骤4：提交当前交易（cardborder=I），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M54" s="38" t="inlineStr">
@@ -12309,9 +12398,18 @@
       </c>
       <c r="L55" s="38" t="inlineStr">
         <is>
-          <t>步骤1：当前笔cardborder=L（本地卡）
-步骤2：★ 预期失败条件：条件6，cardborder=L ≠ I ✗
-步骤3：提交当前交易，进入事件历史模块验证预期结果</t>
+          <t>步骤1：准备1个商户M1，MCC=5999（不在排除列表）
+步骤2：构造近30天和近2h历史交易满足条件1-5、7
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件6（当前笔为境外卡）
+  - 条件1：近30天境外卡占比 ≤ 20% ✓
+  - 条件2：近30天总销售金额 ≥ 50000 ✓
+  - 条件3：近2h境外卡金额占总金额 ≥ 70% ✓
+  - 条件4：近2h境外卡笔数 ≥ 5 ✓
+  - 条件5：近2h境外卡金额 ≥ 20000 ✓
+  - 条件6：当前笔cardborder = L（本地卡，不等于I）✗
+  - 条件7：当前笔MCC ∉ 排除列表 ✓
+步骤4：提交当前交易（cardborder=L），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M55" s="38" t="inlineStr">
@@ -12652,9 +12750,18 @@
       </c>
       <c r="L56" s="38" t="inlineStr">
         <is>
-          <t>步骤1：当前笔MCC=7011（酒店，在排除列表中）
-步骤2：★ 预期失败条件：条件7 ✗
-步骤3：提交当前交易，进入事件历史模块验证预期结果</t>
+          <t>步骤1：准备1个商户M1，MCC=7011（酒店，在排除列表中）
+步骤2：构造近30天和近2h历史交易满足条件1-6
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件7（MCC不在排除列表）
+  - 条件1：近30天境外卡占比 ≤ 20% ✓
+  - 条件2：近30天总销售金额 ≥ 50000 ✓
+  - 条件3：近2h境外卡金额占总金额 ≥ 70% ✓
+  - 条件4：近2h境外卡笔数 ≥ 5 ✓
+  - 条件5：近2h境外卡金额 ≥ 20000 ✓
+  - 条件6：当前笔cardborder = I ✓
+  - 条件7：当前笔MCC=7011 ∈ 排除列表 ✗
+步骤4：提交当前交易（cardborder=I，MCC=7011），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M56" s="38" t="inlineStr">
@@ -13218,7 +13325,14 @@
       </c>
       <c r="L59" s="38" t="inlineStr">
         <is>
-          <t>★ 预期失败条件：条件2，银行卡数(7) &lt; 8 ✗</t>
+          <t>步骤1：准备1个终端T1，商户不在ACQ_KEYMERCHANTS名单内
+步骤2：构造近2小时同金额(500PHP)线下销售交易15笔，仅7张不同银行卡（不满足8张要求）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（同终端同金额银行卡数≥8）
+  - 条件1：同终端同金额(≥500)笔数(15) ≥ 15 ✓
+  - 条件2：同终端同金额银行卡数(7) &lt; 8 ✗
+  - 条件3-4：不满足条件2，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M59" s="38" t="inlineStr">
@@ -13383,7 +13497,15 @@
       </c>
       <c r="L60" s="38" t="inlineStr">
         <is>
-          <t>★ 预期失败条件：条件3，当前笔金额(499) &lt; 500 ✗</t>
+          <t>步骤1：准备1个终端T1，商户不在ACQ_KEYMERCHANTS名单内
+步骤2：构造近2小时同金额(499PHP)线下销售交易15笔，8张不同银行卡
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（当前笔金额≥500）
+  - 条件1：同终端同金额(≥500)笔数(15) ≥ 15 ✓
+  - 条件2：同终端同金额银行卡数(8) ≥ 8 ✓
+  - 条件3：当前笔金额(499) &lt; 500 ✗
+  - 条件4：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前交易（amount=499），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M60" s="38" t="inlineStr">
@@ -13548,7 +13670,15 @@
       </c>
       <c r="L61" s="38" t="inlineStr">
         <is>
-          <t>★ 预期失败条件：条件4，merchantName ∈ ACQ_KEYMERCHANTS ✗</t>
+          <t>步骤1：准备1个终端T1，商户merchantName ∈ ACQ_KEYMERCHANTS名单
+步骤2：构造近2小时同金额(500PHP)线下销售交易满足条件1-3
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（merchantName不在名单内）
+  - 条件1：同终端同金额(≥500)笔数 ≥ 15 ✓
+  - 条件2：同终端同金额银行卡数 ≥ 8 ✓
+  - 条件3：当前笔金额(500) ≥ 500 ✓
+  - 条件4：当前笔merchantName ∈ ACQ_KEYMERCHANTS ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M61" s="38" t="inlineStr">
@@ -13720,8 +13850,13 @@
   - 9笔整千数倍(IS1000INT=1，如1000PHP)销售交易：5张不同银行卡
   - 当前笔：IS1000INT=1，金额=1000
   （整千笔数10≥10✓；银行卡数5≥5✓）
-步骤3：验证各条件：整千笔数(10)≥10✓；银行卡数(5)≥5✓；当前笔IS1000INT=1✓；MCC=5999✓；merchantName∉名单✓
-步骤4：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：近2h整千数倍销售笔数(10) ≥ 10 ✓
+  - 条件2：近2h整千数倍银行卡数(5) ≥ 5 ✓
+  - 条件3：当前笔IS1000INT = 1 ✓
+  - 条件4：当前笔MCC=5999 ∉ 排除列表 ✓
+  - 条件5：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M62" s="36" t="inlineStr">
@@ -14172,7 +14307,14 @@
       </c>
       <c r="L64" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：银行卡数(4) &lt; 5 ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5999（不在排除列表），不在ACQ_KEYMERCHANTS名单
+步骤2：构造近2小时整千数倍销售交易10笔，仅4张不同银行卡（不满足5张要求）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（整千数倍银行卡数≥5）
+  - 条件1：近2h整千数倍销售笔数(10) ≥ 10 ✓
+  - 条件2：近2h整千数倍银行卡数(4) &lt; 5 ✗
+  - 条件3-5：不满足条件2，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M64" s="38" t="inlineStr">
@@ -14339,7 +14481,15 @@
       </c>
       <c r="L65" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3：IS1000INT=0 ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5999（不在排除列表），不在ACQ_KEYMERCHANTS名单
+步骤2：构造近2小时整千数倍销售交易满足条件1-2
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（当前笔IS1000INT=1）
+  - 条件1：近2h整千数倍销售笔数 ≥ 10 ✓
+  - 条件2：近2h整千数倍银行卡数 ≥ 5 ✓
+  - 条件3：当前笔IS1000INT = 0 ≠ 1 ✗
+  - 条件4-5：不满足条件3，不再验证
+步骤4：提交当前交易（IS1000INT=0），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M65" s="38" t="inlineStr">
@@ -14506,7 +14656,16 @@
       </c>
       <c r="L66" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4：MCC=5542 ∈ 排除列表 ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5542（油站，在排除列表中）
+步骤2：构造近2小时整千数倍销售交易满足条件1-3、5
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（MCC不在排除列表）
+  - 条件1：近2h整千数倍销售笔数 ≥ 10 ✓
+  - 条件2：近2h整千数倍银行卡数 ≥ 5 ✓
+  - 条件3：当前笔IS1000INT = 1 ✓
+  - 条件4：当前笔MCC=5542 ∈ 排除列表 ✗
+  - 条件5：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前交易（MCC=5542），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M66" s="38" t="inlineStr">
@@ -14673,7 +14832,16 @@
       </c>
       <c r="L67" s="38" t="inlineStr">
         <is>
-          <t>★ 条件5：merchantName∈ACQ_KEYMERCHANTS ✗</t>
+          <t>步骤1：准备1个商户M1，merchantName ∈ ACQ_KEYMERCHANTS名单
+步骤2：构造近2小时整千数倍销售交易满足条件1-4
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件5（merchantName不在名单内）
+  - 条件1：近2h整千数倍销售笔数 ≥ 10 ✓
+  - 条件2：近2h整千数倍银行卡数 ≥ 5 ✓
+  - 条件3：当前笔IS1000INT = 1 ✓
+  - 条件4：当前笔MCC ∉ 排除列表 ✓
+  - 条件5：当前笔merchantName ∈ ACQ_KEYMERCHANTS ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M67" s="38" t="inlineStr">
@@ -14842,7 +15010,12 @@
 步骤2：构造近2小时历史交易（含当前笔，事中逻辑）：
   - 同商户M1共15笔销售交易，其中同一卡BIN(midbin8=12345678)的有10笔，5张不同卡
   （同卡BIN笔数10≥10✓；银行卡数5≥5✓；同卡BIN笔数10≥总笔数15×0.5=7.5✓）
-步骤3：提交当前笔交易（midbin8=12345678）</t>
+步骤3：验证各条件指标：
+  - 条件1：近2h同卡BIN笔数(10) ≥ 10 ✓
+  - 条件2：近2h同卡BIN银行卡数(5) ≥ 5 ✓
+  - 条件3：同卡BIN笔数(10) ≥ 总笔数(15)×50%=7.5 ✓
+  - 条件4：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前笔交易（midbin8=12345678），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M68" s="36" t="inlineStr">
@@ -15012,7 +15185,13 @@
       </c>
       <c r="L69" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：同卡BIN笔数(9) &lt; 10 ✗</t>
+          <t>步骤1：准备1个商户M1，merchantName不在ACQ_KEYMERCHANTS名单
+步骤2：构造近2小时同卡BIN(midbin8=12345678)销售交易9笔（不满足10笔门槛）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（同卡BIN笔数≥10）
+  - 条件1：近2h同卡BIN笔数(9) &lt; 10 ✗
+  - 条件2-4：不满足入门门槛，不再验证
+步骤4：提交当前交易（midbin8=12345678），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M69" s="38" t="inlineStr">
@@ -15177,7 +15356,14 @@
       </c>
       <c r="L70" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：银行卡数(4) &lt; 5 ✗</t>
+          <t>步骤1：准备1个商户M1，merchantName不在ACQ_KEYMERCHANTS名单
+步骤2：构造近2小时同卡BIN销售交易10笔，仅4张不同银行卡（不满足5张要求）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（同卡BIN银行卡数≥5）
+  - 条件1：近2h同卡BIN笔数(10) ≥ 10 ✓
+  - 条件2：近2h同卡BIN银行卡数(4) &lt; 5 ✗
+  - 条件3-4：不满足条件2，不再验证
+步骤4：提交当前交易（midbin8=12345678），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M70" s="38" t="inlineStr">
@@ -15342,7 +15528,15 @@
       </c>
       <c r="L71" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3：同卡BIN占比(40%) &lt; 50% ✗</t>
+          <t>步骤1：准备1个商户M1，merchantName不在ACQ_KEYMERCHANTS名单
+步骤2：构造近2小时总销售交易20笔，同卡BIN仅8笔（8/20=40%&lt;50%）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（同卡BIN笔数占比≥50%）
+  - 条件1：近2h同卡BIN笔数(8) &lt; 10（但条件1已变为整体约束）✓
+  实际：条件1(8&lt;10)✗，条件3(40%&lt;50%)✗ — 条件1和条件3均失败
+  - 条件2：同卡BIN银行卡数 ≥ 5 ✓
+  - 条件4：merchantName ∉ 名单 ✓
+步骤4：提交当前交易（midbin8=12345678），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M71" s="38" t="inlineStr">
@@ -15540,7 +15734,15 @@
       </c>
       <c r="L72" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4：merchantName∈ACQ_KEYMERCHANTS ✗</t>
+          <t>步骤1：准备1个商户M1，merchantName ∈ ACQ_KEYMERCHANTS名单
+步骤2：构造近2小时同卡BIN销售交易满足条件1-3
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（merchantName不在名单内）
+  - 条件1：近2h同卡BIN笔数 ≥ 10 ✓
+  - 条件2：近2h同卡BIN银行卡数 ≥ 5 ✓
+  - 条件3：同卡BIN笔数占比 ≥ 50% ✓
+  - 条件4：当前笔merchantName ∈ ACQ_KEYMERCHANTS ✗
+步骤4：提交当前交易（midbin8=12345678），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M72" s="38" t="inlineStr">
@@ -15714,7 +15916,14 @@
   - 2笔凌晨线下(posEntryMode=C)大额(≥500)销售交易（bizhour=2,3）
   - 当前笔：amount=500，bizhour=2，posEntryMode=C
   （笔数3≥3✓；当前笔金额500≥500✓；bizhour=2∈[1,5)✓）
-步骤3：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：近1天凌晨大额线下笔数(3) ≥ 3 ✓
+  - 条件2：当前笔金额(500) ≥ 500 ✓
+  - 条件3：当前笔bizhour=2 ∈ [1,5) ✓
+  - 条件4：当前笔posEntryMode=C ∈ 线下列表 ✓
+  - 条件5：当前笔MCC=5999 ∉ 白名单 ✓
+  - 条件6：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M73" s="36" t="inlineStr">
@@ -15971,7 +16180,13 @@
       </c>
       <c r="L74" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：笔数(2) &lt; 3 ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5999，不在白名单，不在ACQ_KEYMERCHANTS
+步骤2：构造近1天凌晨1-5点大额线下(posEntryMode=C)销售交易2笔（不满足3笔门槛）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（凌晨大额线下笔数≥3）
+  - 条件1：近1天凌晨大额线下笔数(2) &lt; 3 ✗
+  - 条件2-6：不满足入门门槛，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M74" s="38" t="inlineStr">
@@ -16165,7 +16380,17 @@
       </c>
       <c r="L75" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：金额(499) &lt; 500 ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5999，不在白名单，不在ACQ_KEYMERCHANTS
+步骤2：构造近1天凌晨大额线下销售交易满足条件1、3-6
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（当前笔金额≥500）
+  - 条件1：近1天凌晨大额线下笔数 ≥ 3 ✓
+  - 条件2：当前笔金额(499) &lt; 500 ✗
+  - 条件3：当前笔bizhour=2 ∈ [1,5) ✓
+  - 条件4：当前笔posEntryMode=C ∈ 线下列表 ✓
+  - 条件5：当前笔MCC ∉ 白名单 ✓
+  - 条件6：当前笔merchantName ∉ 名单 ✓
+步骤4：提交当前交易（amount=499），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M75" s="38" t="inlineStr">
@@ -16388,7 +16613,17 @@
       </c>
       <c r="L76" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3：bizhour=6 ∉ [1,5) ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5999，不在白名单，不在ACQ_KEYMERCHANTS
+步骤2：构造近1天凌晨大额线下销售交易满足条件1-2、4-6
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（bizhour在凌晨1-5点）
+  - 条件1：近1天凌晨大额线下笔数 ≥ 3 ✓
+  - 条件2：当前笔金额(500) ≥ 500 ✓
+  - 条件3：当前笔bizhour=6 ∉ [1,5) ✗
+  - 条件4：当前笔posEntryMode=C ∈ 线下列表 ✓
+  - 条件5：当前笔MCC ∉ 白名单 ✓
+  - 条件6：当前笔merchantName ∉ 名单 ✓
+步骤4：提交当前交易（bizhour=6），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M76" s="38" t="inlineStr">
@@ -16640,7 +16875,17 @@
       </c>
       <c r="L77" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4：posEntryMode=E ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5999，不在白名单，不在ACQ_KEYMERCHANTS
+步骤2：构造近1天凌晨大额线下销售交易满足条件1-3、5-6
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（当前笔posEntryMode在线下列表中）
+  - 条件1：近1天凌晨大额线下笔数 ≥ 3 ✓
+  - 条件2：当前笔金额(500) ≥ 500 ✓
+  - 条件3：当前笔bizhour=2 ∈ [1,5) ✓
+  - 条件4：当前笔posEntryMode=E ∉ 线下列表 ✗
+  - 条件5：当前笔MCC ∉ 白名单 ✓
+  - 条件6：当前笔merchantName ∉ 名单 ✓
+步骤4：提交当前交易（posEntryMode=E），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M77" s="38" t="inlineStr">
@@ -16863,7 +17108,17 @@
       </c>
       <c r="L78" s="38" t="inlineStr">
         <is>
-          <t>★ 条件5：MCC=5542 ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5542（油站，在白名单内）
+步骤2：构造近1天凌晨大额线下销售交易满足条件1-4、6
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件5（MCC不在白名单）
+  - 条件1：近1天凌晨大额线下笔数 ≥ 3 ✓
+  - 条件2：当前笔金额(500) ≥ 500 ✓
+  - 条件3：当前笔bizhour=2 ∈ [1,5) ✓
+  - 条件4：当前笔posEntryMode在线下列表中 ✓
+  - 条件5：当前笔MCC=5542 ∈ 白名单 ✗
+  - 条件6：当前笔merchantName ∉ 名单 ✓
+步骤4：提交当前交易（MCC=5542），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M78" s="38" t="inlineStr">
@@ -17115,7 +17370,17 @@
       </c>
       <c r="L79" s="38" t="inlineStr">
         <is>
-          <t>★ 条件6：merchantName∈ACQ_KEYMERCHANTS ✗</t>
+          <t>步骤1：准备1个商户M1，merchantName ∈ ACQ_KEYMERCHANTS名单
+步骤2：构造近1天凌晨大额线下销售交易满足条件1-5
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件6（merchantName不在名单内）
+  - 条件1：近1天凌晨大额线下笔数 ≥ 3 ✓
+  - 条件2：当前笔金额(500) ≥ 500 ✓
+  - 条件3：当前笔bizhour=2 ∈ [1,5) ✓
+  - 条件4：当前笔posEntryMode在线下列表中 ✓
+  - 条件5：当前笔MCC ∉ 白名单 ✓
+  - 条件6：当前笔merchantName ∈ ACQ_KEYMERCHANTS ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M79" s="38" t="inlineStr">
@@ -17339,7 +17604,12 @@
   - 2笔大额(≥1000PHP)销售交易
   - 当前笔：amount=1000
   （大额笔数3≥3✓；当前笔金额1000≥1000✓）
-步骤3：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：近1天该商户大额笔数(3) ≥ 3 ✓
+  - 条件2：当前笔金额(1000) ≥ 1000 ✓
+  - 条件3：当前笔MCC ∈ ACQ_LOWVALUEMCC ✓
+  - 条件4：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M80" s="36" t="inlineStr">
@@ -17592,7 +17862,13 @@
       </c>
       <c r="L81" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：大额笔数(2) &lt; 3 ✗</t>
+          <t>步骤1：准备1个商户M1，MCC在ACQ_LOWVALUEMCC名单，不在ACQ_KEYMERCHANTS
+步骤2：构造近1天大额(≥1000PHP)销售交易2笔（不满足3笔门槛）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（大额笔数≥3）
+  - 条件1：近1天该商户大额笔数(2) &lt; 3 ✗
+  - 条件2-4：不满足入门门槛，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M81" s="38" t="inlineStr">
@@ -17782,7 +18058,15 @@
       </c>
       <c r="L82" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：金额(999) &lt; 1000 ✗</t>
+          <t>步骤1：准备1个商户M1，MCC在ACQ_LOWVALUEMCC名单，不在ACQ_KEYMERCHANTS
+步骤2：构造近1天大额销售交易满足条件1、3-4
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（当前笔金额≥1000）
+  - 条件1：近1天该商户大额笔数 ≥ 3 ✓
+  - 条件2：当前笔金额(999) &lt; 1000 ✗
+  - 条件3：当前笔MCC ∈ ACQ_LOWVALUEMCC ✓
+  - 条件4：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前交易（amount=999），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M82" s="38" t="inlineStr">
@@ -18030,7 +18314,15 @@
       </c>
       <c r="L83" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3：MCC不在ACQ_LOWVALUEMCC ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5999（不在ACQ_LOWVALUEMCC名单），不在ACQ_KEYMERCHANTS
+步骤2：构造近1天大额销售交易满足条件1-2、4
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（MCC在ACQ_LOWVALUEMCC名单中）
+  - 条件1：近1天该商户大额笔数 ≥ 3 ✓
+  - 条件2：当前笔金额(1000) ≥ 1000 ✓
+  - 条件3：当前笔MCC=5999 ∉ ACQ_LOWVALUEMCC ✗
+  - 条件4：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前交易（MCC=5999），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M83" s="38" t="inlineStr">
@@ -18278,7 +18570,15 @@
       </c>
       <c r="L84" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4 ✗</t>
+          <t>步骤1：准备1个商户M1，merchantName ∈ ACQ_KEYMERCHANTS名单，MCC在ACQ_LOWVALUEMCC
+步骤2：构造近1天大额销售交易满足条件1-3
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（merchantName不在名单内）
+  - 条件1：近1天该商户大额笔数 ≥ 3 ✓
+  - 条件2：当前笔金额(1000) ≥ 1000 ✓
+  - 条件3：当前笔MCC ∈ ACQ_LOWVALUEMCC ✓
+  - 条件4：当前笔merchantName ∈ ACQ_KEYMERCHANTS ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M84" s="38" t="inlineStr">
@@ -18497,8 +18797,11 @@
         <is>
           <t>步骤1：准备1个商户M1，MCC=5462（烘焙），不在ACQ_KEYMERCHANTS
 步骤2：当前笔amount=1000
-步骤3：MCC=5462∈{5462,7210,7523}✓；金额1000≥1000✓；merchantName∉名单✓
-步骤4：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：当前笔MCC=5462 ∈ {5462,7210,7523} ✓
+  - 条件2：当前笔金额(1000) ≥ 1000 ✓
+  - 条件3：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M85" s="36" t="inlineStr">
@@ -18632,7 +18935,14 @@
       </c>
       <c r="L86" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：MCC=5999 ∉ {5462,7210,7523} ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5999（不在特定列表中），不在ACQ_KEYMERCHANTS
+步骤2：当前笔amount=1000
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（MCC在{5462,7210,7523}中）
+  - 条件1：当前笔MCC=5999 ∉ {5462,7210,7523} ✗
+  - 条件2：当前笔金额(1000) ≥ 1000 ✓
+  - 条件3：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前交易（MCC=5999），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M86" s="38" t="inlineStr">
@@ -18761,7 +19071,14 @@
       </c>
       <c r="L87" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：金额(999) &lt; 1000 ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5462（烘焙），不在ACQ_KEYMERCHANTS
+步骤2：当前笔amount=999
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（当前笔金额≥1000）
+  - 条件1：当前笔MCC=5462 ∈ {5462,7210,7523} ✓
+  - 条件2：当前笔金额(999) &lt; 1000 ✗
+  - 条件3：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前交易（amount=999），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M87" s="38" t="inlineStr">
@@ -18890,7 +19207,14 @@
       </c>
       <c r="L88" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3：merchantName∈ACQ_KEYMERCHANTS ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5462（烘焙），merchantName ∈ ACQ_KEYMERCHANTS
+步骤2：当前笔amount=1000
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（merchantName不在名单内）
+  - 条件1：当前笔MCC=5462 ∈ {5462,7210,7523} ✓
+  - 条件2：当前笔金额(1000) ≥ 1000 ✓
+  - 条件3：当前笔merchantName ∈ ACQ_KEYMERCHANTS ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M88" s="38" t="inlineStr">
@@ -19021,8 +19345,11 @@
         <is>
           <t>步骤1：准备1个新商户M1，meropendays=90（≤90✓）
 步骤2：当前笔MCC=5499，amount=1000
-步骤3：meropendays(90)≤90✓；MCC=5499✓；金额1000≥1000✓
-步骤4：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：当前笔meropendays(90) ≤ 90 ✓
+  - 条件2：当前笔MCC=5499 ✓
+  - 条件3：当前笔金额(1000) ≥ 1000 ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M89" s="36" t="inlineStr">
@@ -19156,7 +19483,14 @@
       </c>
       <c r="L90" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：meropendays(91) &gt; 90 ✗</t>
+          <t>步骤1：准备1个商户M1，meropendays=91（&gt;90，不属于新商户）
+步骤2：当前笔MCC=5499，amount=1000
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（meropendays≤90）
+  - 条件1：当前笔meropendays(91) &gt; 90 ✗
+  - 条件2：当前笔MCC=5499 ✓
+  - 条件3：当前笔金额(1000) ≥ 1000 ✓
+步骤4：提交当前交易（meropendays=91），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M90" s="38" t="inlineStr">
@@ -19285,7 +19619,14 @@
       </c>
       <c r="L91" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：MCC=5999 ≠ 5499 ✗</t>
+          <t>步骤1：准备1个新商户M1，meropendays=90
+步骤2：当前笔MCC=5999（≠5499），amount=1000
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（MCC=5499）
+  - 条件1：当前笔meropendays(90) ≤ 90 ✓
+  - 条件2：当前笔MCC=5999 ≠ 5499 ✗
+  - 条件3：当前笔金额(1000) ≥ 1000 ✓
+步骤4：提交当前交易（MCC=5999），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M91" s="38" t="inlineStr">
@@ -19414,7 +19755,14 @@
       </c>
       <c r="L92" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3：金额(999) &lt; 1000 ✗</t>
+          <t>步骤1：准备1个新商户M1，meropendays=90
+步骤2：当前笔MCC=5499，amount=999
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（当前笔金额≥1000）
+  - 条件1：当前笔meropendays(90) ≤ 90 ✓
+  - 条件2：当前笔MCC=5499 ✓
+  - 条件3：当前笔金额(999) &lt; 1000 ✗
+步骤4：提交当前交易（amount=999），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M92" s="38" t="inlineStr">
@@ -19549,8 +19897,13 @@
         <is>
           <t>步骤1：准备1个商户M1，近90天排除近1天有30笔销售，平均单笔200PHP，MCC=5999
 步骤2：当前笔amount=1500（≥200×3=600✓；≥1500✓）
-步骤3：历史笔数30≥30✓；金额1500≥1500✓；MCC∉排除列表✓；merchantName∉名单✓
-步骤4：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：当前笔金额(1500) ≥ 近90天ATV(200)×3=600 ✓
+  - 条件2：近90天历史笔数(30) ≥ 30 ✓
+  - 条件3：当前笔金额(1500) ≥ 1500 ✓
+  - 条件4：当前笔MCC ∉ 排除列表 ✓
+  - 条件5：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M93" s="36" t="inlineStr">
@@ -19722,7 +20075,15 @@
       </c>
       <c r="L94" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：金额(500) &lt; 600 ✗</t>
+          <t>步骤1：准备1个商户M1，近90天ATV=200PHP，历史笔数30，MCC=5999（不在排除列表/名单）
+步骤2：当前笔amount=500（&lt;200×3=600）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（当前笔金额≥ATV×3）
+  - 条件1：当前笔金额(500) &lt; 200×3=600 ✗
+  - 条件2：近90天历史笔数(30) ≥ 30 ✓
+  - 条件3：当前笔金额(500) &lt; 1500 ✗
+  - 条件4-5：不满足条件1，不再验证
+步骤4：提交当前交易（amount=500），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M94" s="38" t="inlineStr">
@@ -19889,7 +20250,14 @@
       </c>
       <c r="L95" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：历史笔数(29) &lt; 30 ✗</t>
+          <t>步骤1：准备1个商户M1，近90天ATV=200PHP，历史笔数29（&lt;30），MCC=5999
+步骤2：当前笔amount=1500
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（历史笔数≥30）
+  - 条件1：当前笔金额(1500) ≥ 200×3=600 ✓
+  - 条件2：近90天历史笔数(29) &lt; 30 ✗
+  - 条件3-5：不满足条件2，不再验证
+步骤4：提交当前交易（amount=1500），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M95" s="38" t="inlineStr">
@@ -20056,7 +20424,15 @@
       </c>
       <c r="L96" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3：金额(1499) &lt; 1500 ✗</t>
+          <t>步骤1：准备1个商户M1，近90天ATV=200PHP，历史笔数30，MCC=5999
+步骤2：当前笔amount=1499（&lt;1500）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（当前笔金额≥1500）
+  - 条件1：当前笔金额(1499) ≥ 200×3=600 ✓
+  - 条件2：近90天历史笔数(30) ≥ 30 ✓
+  - 条件3：当前笔金额(1499) &lt; 1500 ✗
+  - 条件4-5：不满足条件3，不再验证
+步骤4：提交当前交易（amount=1499），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M96" s="38" t="inlineStr">
@@ -20252,7 +20628,16 @@
       </c>
       <c r="L97" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4 ✗</t>
+          <t>步骤1：准备1个商户M1，近90天ATV=200PHP，历史笔数30，MCC在排除列表中
+步骤2：构造交易满足条件1-3、5
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（MCC不在排除列表）
+  - 条件1：当前笔金额 ≥ ATV×3 ✓
+  - 条件2：近90天历史笔数 ≥ 30 ✓
+  - 条件3：当前笔金额 ≥ 1500 ✓
+  - 条件4：当前笔MCC ∈ 排除列表 ✗
+  - 条件5：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M97" s="38" t="inlineStr">
@@ -20419,7 +20804,16 @@
       </c>
       <c r="L98" s="38" t="inlineStr">
         <is>
-          <t>★ 条件5 ✗</t>
+          <t>步骤1：准备1个商户M1，merchantName ∈ ACQ_KEYMERCHANTS，近90天ATV=200PHP，历史笔数30，MCC=5999
+步骤2：构造交易满足条件1-4
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件5（merchantName不在名单内）
+  - 条件1：当前笔金额 ≥ ATV×3 ✓
+  - 条件2：近90天历史笔数 ≥ 30 ✓
+  - 条件3：当前笔金额 ≥ 1500 ✓
+  - 条件4：当前笔MCC ∉ 排除列表 ✓
+  - 条件5：当前笔merchantName ∈ ACQ_KEYMERCHANTS ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M98" s="38" t="inlineStr">
@@ -20616,9 +21010,12 @@
         <is>
           <t>步骤1：准备1个商户M1，不在ACQ_KEYMIDS名单
 步骤2：构造近2天排除近1天：总销售20笔，拒绝12笔（12≥20×0.5=10✓）
-步骤3：近1天内高拒绝率标签='Y'笔数=0&lt;1✓
-步骤4：merchantId∉ACQ_KEYMIDS✓
-步骤5：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：近2天排除1天拒绝率(60%) ≥ 50% ✓
+  - 条件2：近2天排除1天总笔数(20) ≥ 10 ✓
+  - 条件3：近1天内高拒绝率标签笔数(0) &lt; 1 ✓
+  - 条件4：当前笔merchantId ∉ ACQ_KEYMIDS ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M99" s="36" t="inlineStr">
@@ -20820,7 +21217,13 @@
       </c>
       <c r="L100" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：拒绝率(40%) &lt; 50% ✗</t>
+          <t>步骤1：准备1个商户M1，不在ACQ_KEYMIDS名单
+步骤2：构造近2天排除近1天：总销售20笔，拒绝8笔（8/20=40%&lt;50%）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（拒绝率≥50%）
+  - 条件1：近2天排除1天拒绝率(40%) &lt; 50% ✗
+  - 条件2-4：不满足条件1，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M100" s="38" t="inlineStr">
@@ -21391,7 +21794,15 @@
       </c>
       <c r="L102" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3：高拒绝率标签笔数(1) ≥ 1 ✗</t>
+          <t>步骤1：准备1个商户M1，不在ACQ_KEYMIDS名单
+步骤2：构造近2天排除近1天满足条件1-2；近1天内有高拒绝率标签笔数=1
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（近1天内高拒绝率标签笔数&lt;1）
+  - 条件1：近2天排除1天拒绝率 ≥ 50% ✓
+  - 条件2：近2天排除1天总笔数 ≥ 10 ✓
+  - 条件3：近1天内高拒绝率标签笔数(1) ≥ 1 ✗
+  - 条件4：当前笔merchantId ∉ ACQ_KEYMIDS ✓
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M102" s="38" t="inlineStr">
@@ -21754,7 +22165,15 @@
       </c>
       <c r="L103" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4 ✗</t>
+          <t>步骤1：准备1个商户M1，merchantId ∈ ACQ_KEYMIDS名单
+步骤2：构造近2天排除近1天满足条件1-3
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（merchantId不在名单内）
+  - 条件1：近2天排除1天拒绝率 ≥ 50% ✓
+  - 条件2：近2天排除1天总笔数 ≥ 10 ✓
+  - 条件3：近1天内高拒绝率标签笔数 &lt; 1 ✓
+  - 条件4：当前笔merchantId ∈ ACQ_KEYMIDS ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M103" s="38" t="inlineStr">
@@ -21954,9 +22373,13 @@
       <c r="L104" s="36" t="inlineStr">
         <is>
           <t>步骤1：准备1个商户M1
-步骤2：构造近1小时预授权交易：总30笔，拒绝22笔(≥30×0.7=21✓)，银行卡数10≥10✓
-步骤3：当前笔transactionType=P ✓
-步骤4：提交当前笔交易</t>
+步骤2：构造近1小时预授权(transactionType=P)交易：总30笔，拒绝22笔(≥30×0.7=21✓)，银行卡数10≥10✓
+步骤3：验证各条件指标：
+  - 条件1：近1h预授权总笔数(30) ≥ 30 ✓
+  - 条件2：近1h预授权拒绝率(73.3%) ≥ 70% ✓
+  - 条件3：近1h预授权银行卡数(10) ≥ 10 ✓
+  - 条件4：当前笔transactionType = P ✓
+步骤4：提交当前笔交易（transactionType=P），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M104" s="36" t="inlineStr">
@@ -22409,7 +22832,14 @@
       </c>
       <c r="L106" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：拒绝率(60%) &lt; 70% ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近1小时预授权交易30笔，拒绝18笔（18/30=60%&lt;70%），银行卡数10
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（预授权拒绝率≥70%）
+  - 条件1：近1h预授权总笔数(30) ≥ 30 ✓
+  - 条件2：近1h预授权拒绝率(60%) &lt; 70% ✗
+  - 条件3-4：不满足条件2，不再验证
+步骤4：提交当前交易（transactionType=P），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M106" s="38" t="inlineStr">
@@ -22606,7 +23036,15 @@
       </c>
       <c r="L107" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3：银行卡数(9) &lt; 10 ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近1小时预授权交易满足条件1-2，但仅9张不同银行卡
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（预授权银行卡数≥10）
+  - 条件1：近1h预授权总笔数 ≥ 30 ✓
+  - 条件2：近1h预授权拒绝率 ≥ 70% ✓
+  - 条件3：近1h预授权银行卡数(9) &lt; 10 ✗
+  - 条件4：当前笔transactionType = P ✓
+步骤4：提交当前交易（transactionType=P），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M107" s="38" t="inlineStr">
@@ -22803,7 +23241,15 @@
       </c>
       <c r="L108" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4：transactionType=M ≠ P ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近1小时预授权交易满足条件1-3
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（当前笔transactionType=P）
+  - 条件1：近1h预授权总笔数 ≥ 30 ✓
+  - 条件2：近1h预授权拒绝率 ≥ 70% ✓
+  - 条件3：近1h预授权银行卡数 ≥ 10 ✓
+  - 条件4：当前笔transactionType = M（销售，不等于P）✗
+步骤4：提交当前交易（transactionType=M），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M108" s="38" t="inlineStr">
@@ -23829,8 +24275,10 @@
         <is>
           <t>步骤1：准备1个商户M1，不在ACQ_KEYMIDS名单
 步骤2：当前笔MCC=7995（博彩类，∈{7995,6051,6211}）
-步骤3：merchantId∉ACQ_KEYMIDS✓；MCC=7995∈{7995,6051,6211}✓
-步骤4：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：当前笔merchantId ∉ ACQ_KEYMIDS ✓
+  - 条件2：当前笔MCC=7995 ∈ {7995,6051,6211} ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M113" s="36" t="inlineStr">
@@ -23962,7 +24410,13 @@
       </c>
       <c r="L114" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1 ✗</t>
+          <t>步骤1：准备1个商户M1，merchantId ∈ ACQ_KEYMIDS名单
+步骤2：当前笔MCC=7995（博彩类）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（merchantId不在名单内）
+  - 条件1：当前笔merchantId ∈ ACQ_KEYMIDS ✗
+  - 条件2：当前笔MCC=7995 ∈ {7995,6051,6211} ✓
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M114" s="38" t="inlineStr">
@@ -24089,7 +24543,13 @@
       </c>
       <c r="L115" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：MCC=5999 ∉ {7995,6051,6211} ✗</t>
+          <t>步骤1：准备1个商户M1，不在ACQ_KEYMIDS名单
+步骤2：当前笔MCC=5999（非博彩类，∉{7995,6051,6211}）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（MCC在博彩类列表中）
+  - 条件1：当前笔merchantId ∉ ACQ_KEYMIDS ✓
+  - 条件2：当前笔MCC=5999 ∉ {7995,6051,6211} ✗
+步骤4：提交当前交易（MCC=5999），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M115" s="38" t="inlineStr">
@@ -24222,8 +24682,13 @@
         <is>
           <t>步骤1：准备1个新商户M1，meropendays=90（≤90），不在ACQ_KEYMERCHANTS
 步骤2：构造近1天销售交易（含当前笔，事中逻辑）：笔数51&gt;50✓，金额15000&lt;20000
-步骤3：（C1成立，C3成立，C4成立）→ 规则触发
-步骤4：提交当前笔交易</t>
+  （走C1路径：笔数突增）
+步骤3：验证各条件指标：
+  - 条件1 (C1)：近1天销售笔数(51) &gt; 50 ✓ → 走分支A
+  - 条件3 (C3)：meropendays(90) ≤ 90 ✓
+  - 条件4 (C4)：merchantName ∉ ACQ_KEYMERCHANTS ✓
+  - 规则触发：C1∧C3∧C4成立
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M116" s="36" t="inlineStr">
@@ -24746,7 +25211,14 @@
       </c>
       <c r="L119" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3：meropendays(91) &gt; 90 ✗</t>
+          <t>步骤1：准备1个商户M1，meropendays=91（&gt;90，非新商户），不在ACQ_KEYMERCHANTS
+步骤2：构造近1天销售交易满足C1或C2
+步骤3：验证各条件指标：
+  ★ 预期失败条件：C3（meropendays≤90）
+  - C1/C2：可能满足 ✓
+  - C3：meropendays(91) &gt; 90 ✗
+  - C4：merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前交易（meropendays=91），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M119" s="38" t="inlineStr">
@@ -24916,7 +25388,14 @@
       </c>
       <c r="L120" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4 ✗</t>
+          <t>步骤1：准备1个新商户M1，meropendays=90，merchantName ∈ ACQ_KEYMERCHANTS
+步骤2：构造近1天销售交易满足C1或C2、C3
+步骤3：验证各条件指标：
+  ★ 预期失败条件：C4（merchantName不在名单内）
+  - C1/C2：满足 ✓
+  - C3：meropendays(90) ≤ 90 ✓
+  - C4：merchantName ∈ ACQ_KEYMERCHANTS ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M120" s="38" t="inlineStr">
@@ -25087,7 +25566,11 @@
         <is>
           <t>步骤1：准备1个新商户M1，meropendays=90≤90
 步骤2：构造近90天：总销售30笔，拒绝12笔(≥30×0.3=9✓)
-步骤3：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：近90天总销售笔数 ≥ 30 ✓
+  - 条件2：近90天拒绝率(40%) ≥ 30% ✓
+  - 条件3：meropendays(90) ≤ 90 ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M121" s="36" t="inlineStr">
@@ -25294,7 +25777,13 @@
       </c>
       <c r="L122" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1 ✗</t>
+          <t>步骤1：准备1个新商户M1，meropendays=90
+步骤2：构造近90天总销售29笔（&lt;30），拒绝12笔
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（近90天总销售笔数≥30）
+  - 条件1：近90天总销售笔数(29) &lt; 30 ✗
+  - 条件2-3：不满足入门门槛，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M122" s="38" t="inlineStr">
@@ -25806,7 +26295,14 @@
       </c>
       <c r="L124" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3 ✗</t>
+          <t>步骤1：准备1个商户M1，meropendays=91（&gt;90，非新商户）
+步骤2：构造近90天总销售30笔，拒绝12笔满足条件1-2
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（meropendays≤90）
+  - 条件1：近90天总销售笔数 ≥ 30 ✓
+  - 条件2：近90天拒绝率(40%) ≥ 30% ✓
+  - 条件3：meropendays(91) &gt; 90 ✗
+步骤4：提交当前交易（meropendays=91），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M124" s="38" t="inlineStr">
@@ -26011,8 +26507,12 @@
         <is>
           <t>步骤1：准备1个新商户M1，meropendays=90≤90
 步骤2：近90天排除1天：日最高笔数=20（≥10✓）；近1天笔数=100（≥20×5=100✓）
-步骤3：C1∧C2成立 → 走分支A；C5成立（meropendays≤90）→ 规则触发
-步骤4：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - C1：近90天排除1天日最高笔数(20) ≥ 10 ✓
+  - C2：近1天笔数(100) ≥ 20×5=100 ✓ → 走分支A
+  - C5：meropendays(90) ≤ 90 ✓
+  - 规则触发：C1∧C2∧C5成立
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M125" s="36" t="inlineStr">
@@ -26639,7 +27139,13 @@
       </c>
       <c r="L128" s="38" t="inlineStr">
         <is>
-          <t>★ 条件5：meropendays(91) &gt; 90 ✗</t>
+          <t>步骤1：准备1个商户M1，meropendays=91（&gt;90，非新商户）
+步骤2：构造历史交易满足分支A或分支B
+步骤3：验证各条件指标：
+  ★ 预期失败条件：C5（meropendays≤90）
+  - 分支A/B：可能满足 ✓
+  - C5：meropendays(91) &gt; 90 ✗
+步骤4：提交当前交易（meropendays=91），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M128" s="38" t="inlineStr">
@@ -27358,7 +27864,14 @@
       </c>
       <c r="L131" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2 ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近1天整千金额占比满足条件1，但整千金额=15000&lt;20000
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（整千金额≥20000）
+  - 条件1：近1天整千金额占比 ≥ 50% ✓
+  - 条件2：近1天整千金额(15000) &lt; 20000 ✗
+  - 条件3-4：不满足条件2，不再验证
+步骤4：提交当前交易（IS1000INT=1），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M131" s="38" t="inlineStr">
@@ -27556,7 +28069,15 @@
       </c>
       <c r="L132" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3 ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近1天整千金额满足条件1-2，但整千笔数=9&lt;10
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（整千笔数≥10）
+  - 条件1：近1天整千金额占比 ≥ 50% ✓
+  - 条件2：近1天整千金额 ≥ 20000 ✓
+  - 条件3：近1天整千笔数(9) &lt; 10 ✗
+  - 条件4：当前笔IS1000INT = 1 ✓
+步骤4：提交当前交易（IS1000INT=1），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M132" s="38" t="inlineStr">
@@ -27754,7 +28275,15 @@
       </c>
       <c r="L133" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4：IS1000INT=0 ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近1天整千数交易满足条件1-3
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（当前笔IS1000INT=1）
+  - 条件1：近1天整千金额占比 ≥ 50% ✓
+  - 条件2：近1天整千金额 ≥ 20000 ✓
+  - 条件3：近1天整千笔数 ≥ 10 ✓
+  - 条件4：当前笔IS1000INT = 0 ≠ 1 ✗
+步骤4：提交当前交易（IS1000INT=0），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M133" s="38" t="inlineStr">
@@ -27956,7 +28485,13 @@
         <is>
           <t>步骤1：准备1个商户M1，近30天ATV=300PHP，同MCC ATV=100PHP（300≥100×3=300✓）
 步骤2：商户近30天笔数50≥50✓；金额50000≥50000✓；同MCC笔数500≥500✓
-步骤3：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - C1：商户ATV(300) ≥ 同MCC ATV(100)×3=300 ✓ → 走分支A
+  - 条件3：近30天商户笔数(50) ≥ 50 ✓
+  - 条件4：近30天商户金额(50000) ≥ 50000 ✓
+  - 条件5：近30天同MCC笔数(500) ≥ 500 ✓
+  - 规则触发：C1∧C3∧C4∧C5成立
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M134" s="36" t="inlineStr">
@@ -28168,7 +28703,13 @@
         <is>
           <t>步骤1：准备1个商户M1，近30天ATV=30PHP，同MCC ATV=100PHP（30≤100×0.3=30✓）
 步骤2：商户近30天笔数50≥50✓；金额50000≥50000✓；同MCC笔数500≥500✓
-步骤3：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - C2：商户ATV(30) ≤ 同MCC ATV(100)×0.3=30 ✓ → 走分支B
+  - 条件3：近30天商户笔数(50) ≥ 50 ✓
+  - 条件4：近30天商户金额(50000) ≥ 50000 ✓
+  - 条件5：近30天同MCC笔数(500) ≥ 500 ✓
+  - 规则触发：C2∧C3∧C4∧C5成立
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M135" s="38" t="inlineStr">
@@ -28378,7 +28919,16 @@
       </c>
       <c r="L136" s="38" t="inlineStr">
         <is>
-          <t>★ C1失败：商户ATV(200) &lt; 300 ✗；C2失败：商户ATV(200) &gt; 30 ✗</t>
+          <t>步骤1：准备1个商户M1，近30天ATV=200PHP，同MCC ATV=100PHP（200&lt;300且200&gt;30）
+步骤2：商户近30天笔数50，金额50000，同MCC笔数500
+步骤3：验证各条件指标：
+  ★ 预期失败条件：C1（ATV≥同MCC×3）和C2（ATV≤同MCC×0.3）均不满足
+  - C1：商户ATV(200) &lt; 100×3=300 ✗
+  - C2：商户ATV(200) &gt; 100×0.3=30 ✗
+  - 条件3：近30天商户笔数(50) ≥ 50 ✓
+  - 条件4：近30天商户金额(50000) ≥ 50000 ✓
+  - 条件5：近30天同MCC笔数(500) ≥ 500 ✓
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M136" s="38" t="inlineStr">
@@ -28582,7 +29132,14 @@
       </c>
       <c r="L137" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3：笔数(49) &lt; 50 ✗</t>
+          <t>步骤1：准备1个商户M1，近30天ATV满足C1或C2，但笔数49&lt;50
+步骤2：近30天金额50000，同MCC笔数500
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（近30天商户笔数≥50）
+  - C1/C2：可能满足 ✓
+  - 条件3：近30天商户笔数(49) &lt; 50 ✗
+  - 条件4-5：不满足条件3，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M137" s="38" t="inlineStr">
@@ -28986,7 +29543,15 @@
       </c>
       <c r="L139" s="38" t="inlineStr">
         <is>
-          <t>★ 条件5：同MCC笔数(499) &lt; 500 ✗</t>
+          <t>步骤1：准备1个商户M1，满足C1/C2、条件3-4，同MCC笔数499&lt;500
+步骤2：近30天商户笔数50，金额50000
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件5（近30天同MCC笔数≥500）
+  - C1/C2：满足 ✓
+  - 条件3：近30天商户笔数 ≥ 50 ✓
+  - 条件4：近30天商户金额 ≥ 50000 ✓
+  - 条件5：近30天同MCC笔数(499) &lt; 500 ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M139" s="38" t="inlineStr">
@@ -29188,7 +29753,12 @@
           <t>步骤1：准备1个商户M1
 步骤2：近30天排除近7天：50笔销售，ATV=500PHP；近7天：20笔销售，ATV=1000PHP
   （1000≥500×2=1000✓；1000≥1000✓；近7天笔数20≥20✓；历史笔数50≥50✓）
-步骤3：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：近7天ATV(1000) ≥ 历史ATV(500)×2=1000 ✓
+  - 条件2：近7天ATV(1000) ≥ 1000 ✓
+  - 条件3：近7天笔数(20) ≥ 20 ✓
+  - 条件4：近30天排除7天历史笔数(50) ≥ 50 ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M140" s="36" t="inlineStr">
@@ -29395,7 +29965,13 @@
       </c>
       <c r="L141" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1 ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近30天排除近7天ATV=500，近7天ATV=800（&lt;500×2=1000）
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（近7天ATV≥历史ATV×2）
+  - 条件1：近7天ATV(800) &lt; 500×2=1000 ✗
+  - 条件2-4：不满足条件1，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M141" s="38" t="inlineStr">
@@ -29597,7 +30173,14 @@
       </c>
       <c r="L142" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2 ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近7天ATV满足条件1（≥1000），但近7天ATV=900&lt;1000
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（近7天ATV≥1000）
+  - 条件1：近7天ATV ≥ 历史ATV×2 ✓
+  - 条件2：近7天ATV(900) &lt; 1000 ✗
+  - 条件3-4：不满足条件2，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M142" s="38" t="inlineStr">
@@ -29795,7 +30378,15 @@
       </c>
       <c r="L143" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3 ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近7天ATV满足条件1-2，近7天笔数19&lt;20
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（近7天笔数≥20）
+  - 条件1：近7天ATV ≥ 历史ATV×2 ✓
+  - 条件2：近7天ATV ≥ 1000 ✓
+  - 条件3：近7天笔数(19) &lt; 20 ✗
+  - 条件4：近30天排除7天历史笔数 ≥ 50 ✓
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M143" s="38" t="inlineStr">
@@ -29997,7 +30588,15 @@
       </c>
       <c r="L144" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4 ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近7天ATV满足条件1-3，近30天排除7天历史笔数49&lt;50
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（历史笔数≥50）
+  - 条件1：近7天ATV ≥ 历史ATV×2 ✓
+  - 条件2：近7天ATV ≥ 1000 ✓
+  - 条件3：近7天笔数 ≥ 20 ✓
+  - 条件4：近30天排除7天历史笔数(49) &lt; 50 ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M144" s="38" t="inlineStr">
@@ -30759,7 +31358,16 @@
       </c>
       <c r="L148" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4：MCC=5542 ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5542（油站，在排除列表中）
+步骤2：构造近7天交易满足条件1-3、5-6
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件4（MCC不在排除列表）
+  - 条件1：近7天总销售金额 ≥ 10000 ✓
+  - 条件2：近7天销售笔数 ≥ 30 ✓
+  - 条件3：近7天敏感时段金额占比 ≥ 30% ✓
+  - 条件4：敏感时段不适用（直接看MCC）= 当前笔MCC=5542 ∈ 排除列表 ✗
+  - 条件5-6：不满足条件4，不再验证
+步骤4：提交当前交易（MCC=5542），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M148" s="38" t="inlineStr">
@@ -30932,7 +31540,17 @@
       </c>
       <c r="L149" s="38" t="inlineStr">
         <is>
-          <t>★ 条件6：bizhour=6 ∉ [1,5) ✗</t>
+          <t>步骤1：准备1个商户M1，MCC=5999，不在ACQ_KEYMERCHANTS
+步骤2：构造近7天交易满足条件1-3、5-6
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件6（当前笔bizhour在敏感时段）
+  - 条件1：近7天总销售金额 ≥ 10000 ✓
+  - 条件2：近7天销售笔数 ≥ 30 ✓
+  - 条件3：近7天敏感时段金额占比 ≥ 30% ✓
+  - 条件4：当前笔bizhour=6 ∉ [1,5) ✗
+  - 条件5：当前笔MCC ∉ 排除列表 ✓
+  - 条件6：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前交易（bizhour=6），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M149" s="38" t="inlineStr">
@@ -31108,8 +31726,14 @@
           <t>步骤1：准备1个成熟商户M1，meropendays&gt;90，MCC=5999，不在ACQ_KEYMERCHANTS
 步骤2：近30天排除近7天日均金额=5000PHP（总金额100000/20天≈5000）；近7天日均=15000PHP≥5000×3=15000✓
   近7天总金额50000≥50000✓；历史总金额100000≥100000✓
-步骤3：meropendays(100)&gt;90✓；MCC∉排除列表✓；merchantName∉名单✓
-步骤4：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：meropendays(100) &gt; 90 ✓
+  - 条件2：近7天日均金额(15000) ≥ 历史日均(5000)×3=15000 ✓
+  - 条件3：近7天总金额(50000) ≥ 50000 ✓
+  - 条件4：历史总金额(100000) ≥ 100000 ✓
+  - 条件5：当前笔MCC=5999 ∉ 排除列表 ✓
+  - 条件6：当前笔merchantName ∉ ACQ_KEYMERCHANTS ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M150" s="36" t="inlineStr">
@@ -31315,7 +31939,13 @@
       </c>
       <c r="L151" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1 ✗</t>
+          <t>步骤1：准备1个成熟商户M1，meropendays&gt;90，MCC=5999，不在ACQ_KEYMERCHANTS
+步骤2：构造近7天日均金额 &lt; 历史日均×3
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（近7天日均≥历史日均×3）
+  - 条件1（实际为条件2）：近7天日均金额 &lt; 历史日均×3 ✗
+  - 其他条件：可能满足但条件1不满足则不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M151" s="38" t="inlineStr">
@@ -31514,7 +32144,13 @@
       </c>
       <c r="L152" s="38" t="inlineStr">
         <is>
-          <t>★ 条件4：meropendays(80) ≤ 90 ✗</t>
+          <t>步骤1：准备1个商户M1，meropendays=80（≤90，非成熟商户），MCC=5999
+步骤2：构造交易满足其他条件
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（meropendays&gt;90）
+  - 条件1：meropendays(80) ≤ 90 ✗
+  - 条件2-6：不满足入门门槛，不再验证
+步骤4：提交当前交易（meropendays=80），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M152" s="38" t="inlineStr">
@@ -31713,7 +32349,14 @@
       </c>
       <c r="L153" s="38" t="inlineStr">
         <is>
-          <t>★ 条件6：MCC=7011 ✗</t>
+          <t>步骤1：准备1个成熟商户M1，meropendays&gt;90，MCC=7011（酒店，在排除列表中）
+步骤2：构造交易满足条件1-5
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件6（MCC不在排除列表）
+  - 条件1：meropendays &gt; 90 ✓
+  - 条件2-5：满足 ✓
+  - 条件6：当前笔MCC=7011 ∈ 排除列表 ✗
+步骤4：提交当前交易（MCC=7011），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M153" s="38" t="inlineStr">
@@ -31937,8 +32580,11 @@
         <is>
           <t>步骤1：准备1个客户账户A1，近30天关联商户数3≥3✓
 步骤2：近1天该客户触发'短期交易激增'标签商户数2≥2✓
-步骤3：近1天该客户累计销售金额30000≥30000✓
-步骤4：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：近30天关联商户数(3) ≥ 3 ✓
+  - 条件2：近1天触发激增标签商户数(2) ≥ 2 ✓
+  - 条件3：近1天该客户累计销售金额(30000) ≥ 30000 ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M154" s="36" t="inlineStr">
@@ -32146,7 +32792,13 @@
       </c>
       <c r="L155" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：商户数(2) &lt; 3 ✗</t>
+          <t>步骤1：准备1个客户账户A1，近30天关联商户数2&lt;3
+步骤2：近1天该客户触发激增标签商户数2，累计金额30000
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（关联商户数≥3）
+  - 条件1：近30天关联商户数(2) &lt; 3 ✗
+  - 条件2-3：不满足入门门槛，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M155" s="38" t="inlineStr">
@@ -32309,7 +32961,14 @@
       </c>
       <c r="L156" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：商户数(1) &lt; 2 ✗</t>
+          <t>步骤1：准备1个客户账户A1，近30天关联商户数3，近1天触发激增标签商户数1&lt;2
+步骤2：累计销售金额30000
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（触发激增标签商户数≥2）
+  - 条件1：近30天关联商户数(3) ≥ 3 ✓
+  - 条件2：近1天触发激增标签商户数(1) &lt; 2 ✗
+  - 条件3：近1天该客户累计销售金额 ≥ 30000 ✓
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M156" s="38" t="inlineStr">
@@ -32635,7 +33294,10 @@
         <is>
           <t>步骤1：准备1个商户M1
 步骤2：近30天拒付总笔数6≥6✓；其中VISA欺诈reasoncode(10.1)+MasterCard欺诈(4837)各1笔，欺诈类≥3✓
-步骤3：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：近30天拒付总笔数(6) ≥ 6 ✓
+  - 条件2：近30天欺诈类拒付笔数(3) ≥ 3 ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M158" s="36" t="inlineStr">
@@ -32787,7 +33449,13 @@
       </c>
       <c r="L159" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：拒付笔数(5) &lt; 6 ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近30天拒付总笔数5&lt;6
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（拒付总笔数≥6）
+  - 条件1：近30天拒付总笔数(5) &lt; 6 ✗
+  - 条件2：不满足入门门槛，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M159" s="38" t="inlineStr">
@@ -32974,7 +33642,13 @@
       </c>
       <c r="L160" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：欺诈笔数(2) &lt; 3 ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近30天拒付总笔数6，欺诈类拒付笔数2&lt;3
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（欺诈类拒付笔数≥3）
+  - 条件1：近30天拒付总笔数(6) ≥ 6 ✓
+  - 条件2：近30天欺诈类拒付笔数(2) &lt; 3 ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M160" s="38" t="inlineStr">
@@ -33123,7 +33797,10 @@
         <is>
           <t>步骤1：准备1个新商户M1，meropendays=90≤90
 步骤2：近30天拒付笔数3≥3✓
-步骤3：提交当前笔交易</t>
+步骤3：验证各条件指标：
+  - 条件1：近30天拒付笔数(3) ≥ 3 ✓
+  - 条件2：meropendays(90) ≤ 90 ✓
+步骤4：提交当前笔交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M161" s="36" t="inlineStr">
@@ -33360,7 +34037,13 @@
       </c>
       <c r="L162" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：拒付笔数(2) &lt; 3 ✗</t>
+          <t>步骤1：准备1个新商户M1，meropendays=90≤90
+步骤2：近30天拒付笔数2&lt;3
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（近30天拒付笔数≥3）
+  - 条件1：近30天拒付笔数(2) &lt; 3 ✗
+  - 条件2：meropendays(90) ≤ 90 ✓
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M162" s="38" t="inlineStr">
@@ -33526,7 +34209,13 @@
       </c>
       <c r="L163" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2：meropendays(91) &gt; 90 ✗</t>
+          <t>步骤1：准备1个商户M1，meropendays=91&gt;90（非新商户）
+步骤2：近30天拒付笔数3
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（meropendays≤90）
+  - 条件1：近30天拒付笔数(3) ≥ 3 ✓
+  - 条件2：meropendays(91) &gt; 90 ✗
+步骤4：提交当前交易（meropendays=91），进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M163" s="38" t="inlineStr">
@@ -33993,7 +34682,13 @@
       </c>
       <c r="L165" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：拒付率(7%) &lt; 9% ✗</t>
+          <t>步骤1：准备1个商户M1，近30天销售金额50000
+步骤2：商户拒付率=7%，同MCC拒付率=3%，7%&lt;9%
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（商户拒付率≥同MCC×3）
+  - 条件1：商户拒付率(7%) &lt; 3%×3=9% ✗
+  - 条件2：近30天销售金额(50000) ≥ 50000 ✓
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M165" s="38" t="inlineStr">
@@ -35099,7 +35794,14 @@
       </c>
       <c r="L170" s="38" t="inlineStr">
         <is>
-          <t>★ 条件3 ✗</t>
+          <t>步骤1：准备1个商户M1
+步骤2：构造近1天退款金额10000，退款笔数5，但退款占比40%&lt;50%
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件3（退款占比≥50%）
+  - 条件1：近1天退款金额(10000) ≥ 10000 ✓
+  - 条件2：近1天退款笔数(5) ≥ 5 ✓
+  - 条件3：近1天退款占比(40%) &lt; 50% ✗
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M170" s="38" t="inlineStr">
@@ -35559,7 +36261,13 @@
       </c>
       <c r="L172" s="38" t="inlineStr">
         <is>
-          <t>★ 条件1：退款率(8%) &lt; 10% ✗</t>
+          <t>步骤1：准备1个商户M1，近30天销售金额50000
+步骤2：退款金额4000≥5000？4000&lt;5000，退款率=8%
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件1（退款金额≥销售金额×10%）
+  - 条件1：退款金额(4000) &lt; 50000×10%=5000 ✗
+  - 条件2-3：不满足条件1，不再验证
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M172" s="38" t="inlineStr">
@@ -35813,7 +36521,14 @@
       </c>
       <c r="L173" s="38" t="inlineStr">
         <is>
-          <t>★ 条件2 ✗</t>
+          <t>步骤1：准备1个商户M1，近30天销售金额50000
+步骤2：退款金额5000≥5000✓，商户退款率=10%，同MCC退款率=4%，10%&lt;12%
+步骤3：验证各条件指标：
+  ★ 预期失败条件：条件2（商户退款率≥同MCC×3）
+  - 条件1：退款金额(5000) ≥ 50000×10%=5000 ✓
+  - 条件2：商户退款率(10%) &lt; 4%×3=12% ✗
+  - 条件3：近30天销售金额(50000) ≥ 50000 ✓
+步骤4：提交当前交易，进入事件历史模块验证预期结果</t>
         </is>
       </c>
       <c r="M173" s="38" t="inlineStr">

--- a/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
+++ b/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
@@ -25434,7 +25434,7 @@
     "transactiontime": "12:30:00",
     "externaltransactionid": "EXT_BIZ_ACQ_RS4_000020_0122_G1_H{序号001-051}",
     "merchantid": "M122",
-    "merchantname": "KEY_MERCHANT_001",
+    "merchantname": "KEYMERCHANT001",
     "mcc": "5999",
     "posentrymode": "C",
     "transactionamount": 20001,
@@ -25461,7 +25461,7 @@
   "transactiontime": "14:30:00",
   "externaltransactionid": "EXT_BIZ_ACQ_RS4_000020_0122",
   "merchantid": "M122",
-  "merchantname": "KEY_MERCHANT_001",
+  "merchantname": "KEYMERCHANT001",
   "mcc": "5999",
   "posentrymode": "C",
   "transactionamount": 20001,
@@ -25480,17 +25480,17 @@
       </c>
       <c r="O120" s="38" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P120" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DGHH2UZ1QKYS0QO</t>
+          <t>1785306600000115C267DQ5AS9MMYNJZB8C</t>
         </is>
       </c>
       <c r="Q120" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件3需成立） || 执行结果：规则触发，反案例执行失败（命中规则: ACQ_RS4_000020,ACQ_RS4_000022,ACQ_RS4_000023,ACQ_RS4_000025） 返回报文：120_ACQ_RS4_000020_反案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件3需成立） || 执行结果：目标规则未命中，符合预期 返回报文：120_ACQ_RS4_000020_反案例.json</t>
         </is>
       </c>
     </row>

--- a/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
+++ b/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
@@ -25629,37 +25629,39 @@
    }
   },
   {
-   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
+   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqDecline",
    "批量生成数量": 20,
    "时间窗口": "近90天",
    "bizid规则": "BIZ_ACQ_RS4_000021_0123_G2_H001~H020",
-   "字段分布说明": "2. 近90天: 销售50笔，拒绝20笔(40%)",
+   "字段分布说明": "拒绝事件按AcqDecline接口文档必填字段重建：userdata21=M(AcqSalesFlag)、userdata13=金额、账号用商户(customeracctnumber映射merchantid)",
    "字段分布": [],
    "请求参数模板": {
     "apiModel": 20,
+    "method": 20,
     "bizid": "BIZ_ACQ_RS4_000021_0123_G2_H{序号001-020}",
     "biztime": "2026-07-27 14:30:00",
-    "policyCode": "Acq_Authorization",
+    "policyCode": "Acq_Decline",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
     "transactiondate": "2026-07-27",
     "transactiontime": "14:30:00",
-    "entitytype": "Authorization",
-    "notificationname": "Decline",
+    "eventtype": "AcqDecline",
     "externaltransactionid": "EXT_BIZ_ACQ_RS4_000021_0123_G2_H{序号001-020}",
     "customeridfromheader": "M001",
-    "userdata22": "5999",
-    "userdata23": "C",
+    "customeracctnumber": "5212340000000005",
+    "entitytype": "merchant",
+    "extsource": "kratos",
+    "notificationname": "AcqDeclineNotification",
+    "userdata06": "05",
+    "userdata13": 500,
+    "userdata14": "2026-07-27",
+    "userdata15": "14:30:00",
+    "userdata18": "risk decline test",
     "userdata21": "M",
-    "userdata20": "T123",
-    "userdata24": "D",
-    "userdata27": "V",
-    "userdata19": "5212340000000005",
-    "customeracctnumber": "5212340000000005",
-    "decisioncode": "D",
-    "eventtype": "AcqAuthorization"
-   }
+    "userdata22": "5999"
+   },
+   "账号用商户": true
   }
  ],
  "触发交易(当前笔)": {
@@ -25693,17 +25695,17 @@
       </c>
       <c r="O121" s="44" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>通过</t>
         </is>
       </c>
       <c r="P121" s="38" t="inlineStr">
         <is>
-          <t>1785306600000115C267DXNX1T7UFVR1MVX</t>
+          <t>1785306600000115C267DTH6CZSGAXC9FVG</t>
         </is>
       </c>
       <c r="Q121" s="38" t="inlineStr">
         <is>
-          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件3需成立） || 执行结果：规则未触发，正案例执行失败（命中规则: ACQ_RS4_000020） 返回报文：121_ACQ_RS4_000021_正案例.json</t>
+          <t>已修复：测试数据补齐（来源：语义匹配的183条已执行数据源）；补充aisopendate=20260629（入网天数30天，条件3需成立） || 执行结果：目标规则命中，符合预期 返回报文：121_ACQ_RS4_000021_正案例.json</t>
         </is>
       </c>
     </row>

--- a/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
+++ b/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
@@ -33475,105 +33475,76 @@
         <is>
           <t>{
  "说明": "ACQ_RS4_000031_反案例_反向场景 1：拒付笔数不足6(C1缺) — 反向不触发",
- "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
+ "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
  "历史数据(构造事件历史)": [
   {
    "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
    "时间窗口": "近30天",
-   "请求参数": {
+   "批量生成数量": 4,
+   "字段分布说明": "4笔拒付(&lt;6)破坏C1",
+   "请求参数模板": {
+    "method": 20,
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000031_0168_G1_H001",
-    "biztime": "2026-07-28 14:30:00",
+    "bizid": "BIZ_ROW159_D{序号001-999}",
+    "biztime": "2026-08-07 14:48:47",
     "policyCode": "Acq_Disputes",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:48:47",
     "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000031_0168_G1_H001",
-    "customeridfromheader": "M002",
+    "externaltransactionid": "EXT_BIZ_ROW159_D{序号001-999}",
+    "customeracctnumber": "PLACEHOLDER",
     "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "10.4",
-    "userdata12": 300
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000031_0168_G1_H002",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000031_0168_G1_H002",
-    "customeridfromheader": "M002",
-    "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "10.4",
-    "userdata12": 300
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000031_0168_G1_H003",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000031_0168_G1_H003",
-    "customeridfromheader": "M002",
-    "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "10.4",
-    "userdata12": 300
-   }
+    "userdata01": "10.1",
+    "userdata02": "V",
+    "userdata12": 1000
+   },
+   "账号用商户": true
   }
  ],
  "触发交易(当前笔)": {
   "apiModel": 20,
-  "bizid": "BIZ_ACQ_RS4_000031_0168",
-  "biztime": "2026-07-29 14:30:00",
-  "policyCode": "Acq_Disputes",
+  "bizid": "BIZ_ROW159_C01",
+  "biztime": "2026-08-07 14:53:47",
+  "policyCode": "Acq_Authorization",
   "appCode": "Acquiring",
   "partnerCode": "kratos",
   "orgCode": "hlb_my",
-  "transactiondate": "2026-07-29",
-  "transactiontime": "14:30:00",
-  "eventtype": "AcqDisputes",
-  "externaltransactionid": "EXT_BIZ_ACQ_RS4_000031_0168",
-  "customeridfromheader": "M002",
-  "score1": "5999",
-  "customeracctnumber": "5212340000000005",
-  "userdata01": "10.4",
-  "userdata12": 300
+  "transactiondate": "2026-08-07",
+  "transactiontime": "14:53:47",
+  "externaltransactionid": "EXT_BIZ_ROW159_C01",
+  "merchantid": "M000159",
+  "merchantname": "MERCHANT_TEST",
+  "mcc": "5999",
+  "posentrymode": "C",
+  "transactionamount": 300,
+  "transactiontype": "M",
+  "terminalid": "T000159",
+  "userindicator02": "D",
+  "authsecondaryverify": "V",
+  "cvvverifycode": "V",
+  "paymentinstrumentid": "5212340001590000",
+  "customeracctnumber": "5212340001590000",
+  "transactioncategory": "M"
  }
 }</t>
         </is>
       </c>
       <c r="O159" s="38" t="inlineStr">
         <is>
-          <t>阻塞</t>
-        </is>
-      </c>
-      <c r="P159" s="38" t="n"/>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="P159" s="38" t="inlineStr">
+        <is>
+          <t>1786085627000115C267DIF3TJIJNZWBBHP</t>
+        </is>
+      </c>
       <c r="Q159" s="38" t="inlineStr">
         <is>
-          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共4处，旧地址405） || 执行结果：执行阻塞：接口调用成功，但返回未包含目标规则命中证据 返回报文：159_ACQ_RS4_000031_反案例.json</t>
+          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共4处，旧地址405） || 执行结果：目标规则未命中，符合预期 返回报文：159_ACQ_RS4_000031_反案例.json</t>
         </is>
       </c>
     </row>
@@ -33668,65 +33639,76 @@
         <is>
           <t>{
  "说明": "ACQ_RS4_000031_反案例_反向场景 2：欺诈类拒付不足3(C2缺) — 反向不触发",
- "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
+ "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
  "历史数据(构造事件历史)": [
   {
    "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
+   "时间窗口": "近30天",
    "批量生成数量": 8,
-   "时间窗口": "近30天",
-   "bizid规则": "BIZ_ACQ_RS4_000031_0169_G1_H001~H008",
-   "字段分布说明": "1. 近30天商户M003: 拒付8笔，欺诈类仅2笔",
-   "字段分布": [],
+   "字段分布说明": "8笔普通拒付(≥6满足C1)，欺诈类0笔(&lt;3)破坏C2",
    "请求参数模板": {
+    "method": 20,
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000031_0169_G1_H{序号001-008}",
-    "biztime": "2026-07-28 14:30:00",
+    "bizid": "BIZ_ROW160_D{序号001-999}",
+    "biztime": "2026-08-07 14:48:47",
     "policyCode": "Acq_Disputes",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:48:47",
     "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000031_0169_G1_H{序号001-008}",
-    "customeridfromheader": "M003",
+    "externaltransactionid": "EXT_BIZ_ROW160_D{序号001-999}",
+    "customeracctnumber": "PLACEHOLDER",
     "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "10.4",
-    "userdata12": 300
-   }
+    "userdata01": "10.1",
+    "userdata02": "V",
+    "userdata12": 1000
+   },
+   "账号用商户": true
   }
  ],
  "触发交易(当前笔)": {
   "apiModel": 20,
-  "bizid": "BIZ_ACQ_RS4_000031_0169",
-  "biztime": "2026-07-29 14:30:00",
-  "policyCode": "Acq_Disputes",
+  "bizid": "BIZ_ROW160_C01",
+  "biztime": "2026-08-07 14:53:47",
+  "policyCode": "Acq_Authorization",
   "appCode": "Acquiring",
   "partnerCode": "kratos",
   "orgCode": "hlb_my",
-  "transactiondate": "2026-07-29",
-  "transactiontime": "14:30:00",
-  "eventtype": "AcqDisputes",
-  "externaltransactionid": "EXT_BIZ_ACQ_RS4_000031_0169",
-  "customeridfromheader": "M003",
-  "score1": "5999",
-  "customeracctnumber": "5212340000000005",
-  "userdata01": "10.4",
-  "userdata12": 300
+  "transactiondate": "2026-08-07",
+  "transactiontime": "14:53:47",
+  "externaltransactionid": "EXT_BIZ_ROW160_C01",
+  "merchantid": "M000160",
+  "merchantname": "MERCHANT_TEST",
+  "mcc": "5999",
+  "posentrymode": "C",
+  "transactionamount": 300,
+  "transactiontype": "M",
+  "terminalid": "T000160",
+  "userindicator02": "D",
+  "authsecondaryverify": "V",
+  "cvvverifycode": "V",
+  "paymentinstrumentid": "5212340001600000",
+  "customeracctnumber": "5212340001600000",
+  "transactioncategory": "M"
  }
 }</t>
         </is>
       </c>
       <c r="O160" s="38" t="inlineStr">
         <is>
-          <t>阻塞</t>
-        </is>
-      </c>
-      <c r="P160" s="38" t="n"/>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="P160" s="38" t="inlineStr">
+        <is>
+          <t>1786085627000115C267DHZUYOVNJ78EINT</t>
+        </is>
+      </c>
       <c r="Q160" s="38" t="inlineStr">
         <is>
-          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共2处，旧地址405） || 执行结果：执行阻塞：接口调用成功，但返回未包含目标规则命中证据 返回报文：160_ACQ_RS4_000031_反案例.json</t>
+          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共2处，旧地址405） || 执行结果：目标规则未命中，符合预期 返回报文：160_ACQ_RS4_000031_反案例.json</t>
         </is>
       </c>
     </row>
@@ -33825,150 +33807,77 @@
         <is>
           <t>{
  "说明": "ACQ_RS4_000032_正案例_新商户(入网&lt;=90)+拒付&gt;=3 — 正向触发",
- "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
+ "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
  "历史数据(构造事件历史)": [
   {
    "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
    "时间窗口": "近30天",
-   "请求参数": {
+   "批量生成数量": 4,
+   "账号用商户": true,
+   "字段分布说明": "4笔拒付事件（AcqDisputes，cardscheme=V/reasoncode=10.1），商户维度=customeracctnumber",
+   "请求参数模板": {
+    "method": 20,
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0170_G1_H001",
-    "biztime": "2026-07-28 14:30:00",
+    "bizid": "BIZ_000032_ROW161_H{序号001-099}",
+    "biztime": "2026-08-07 14:31:15",
     "policyCode": "Acq_Disputes",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:31:15",
     "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0170_G1_H001",
-    "customeridfromheader": "M001",
+    "externaltransactionid": "EXT_BIZ_000032_ROW161_H{序号001-099}",
+    "customeracctnumber": "PLACEHOLDER",
     "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0170_G1_H002",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0170_G1_H002",
-    "customeridfromheader": "M001",
-    "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0170_G1_H003",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0170_G1_H003",
-    "customeridfromheader": "M001",
-    "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0170_G1_H004",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0170_G1_H004",
-    "customeridfromheader": "M001",
-    "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0170_G1_H005",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0170_G1_H005",
-    "customeridfromheader": "M001",
-    "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
+    "userdata01": "10.1",
+    "userdata02": "V",
+    "userdata12": 1000
    }
   }
  ],
  "触发交易(当前笔)": {
   "apiModel": 20,
-  "bizid": "BIZ_ACQ_RS4_000032_0170",
-  "biztime": "2026-07-29 14:30:00",
-  "policyCode": "Acq_Disputes",
+  "bizid": "BIZ_000032_ROW161_C01",
+  "biztime": "2026-08-07 14:36:15",
+  "policyCode": "Acq_Authorization",
   "appCode": "Acquiring",
   "partnerCode": "kratos",
   "orgCode": "hlb_my",
-  "transactiondate": "2026-07-29",
-  "transactiontime": "14:30:00",
-  "eventtype": "AcqDisputes",
-  "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0170",
-  "customeridfromheader": "M001",
-  "score1": "5999",
-  "customeracctnumber": "5212340000000005",
-  "userdata01": "13.1",
-  "userdata12": 300,
-  "aisopendate": "20260629"
+  "transactiondate": "2026-08-07",
+  "transactiontime": "14:36:15",
+  "externaltransactionid": "EXT_BIZ_000032_ROW161_C01",
+  "merchantid": "M000161",
+  "merchantname": "MERCHANT_TEST",
+  "mcc": "5999",
+  "posentrymode": "C",
+  "transactionamount": 300,
+  "transactiontype": "M",
+  "terminalid": "T000161",
+  "userindicator02": "D",
+  "authsecondaryverify": "V",
+  "cvvverifycode": "V",
+  "paymentinstrumentid": "5212340001610000",
+  "customeracctnumber": "5212340001610000",
+  "transactioncategory": "M",
+  "aisopendate": "20260708"
  }
 }</t>
         </is>
       </c>
       <c r="O161" s="43" t="inlineStr">
         <is>
-          <t>阻塞</t>
-        </is>
-      </c>
-      <c r="P161" s="38" t="n"/>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="P161" s="38" t="inlineStr">
+        <is>
+          <t>1786084575000115C267DS9O1CWWLJPALPI</t>
+        </is>
+      </c>
       <c r="Q161" s="38" t="inlineStr">
         <is>
-          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共6处，旧地址405）；补充aisopendate=20260629（入网天数30天，条件2需成立） || 执行结果：执行阻塞：接口调用成功，但返回未包含目标规则命中证据 返回报文：161_ACQ_RS4_000032_正案例.json</t>
+          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共6处，旧地址405）；补充aisopendate=20260629（入网天数30天，条件2需成立） || 执行结果：目标规则命中，符合预期 返回报文：161_ACQ_RS4_000032_正案例.json</t>
         </is>
       </c>
     </row>
@@ -34063,84 +33972,77 @@
         <is>
           <t>{
  "说明": "ACQ_RS4_000032_反案例_反向场景 1：拒付笔数不足(C1缺) — 反向不触发",
- "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
+ "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
  "历史数据(构造事件历史)": [
   {
    "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
    "时间窗口": "近30天",
-   "请求参数": {
+   "批量生成数量": 2,
+   "账号用商户": true,
+   "字段分布说明": "2笔拒付事件（AcqDisputes，cardscheme=V/reasoncode=10.1），商户维度=customeracctnumber",
+   "请求参数模板": {
+    "method": 20,
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0171_G1_H001",
-    "biztime": "2026-07-28 14:30:00",
+    "bizid": "BIZ_000032_ROW162_H{序号001-099}",
+    "biztime": "2026-08-07 14:31:15",
     "policyCode": "Acq_Disputes",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:31:15",
     "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0171_G1_H001",
-    "customeridfromheader": "M002",
+    "externaltransactionid": "EXT_BIZ_000032_ROW162_H{序号001-099}",
+    "customeracctnumber": "PLACEHOLDER",
     "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0171_G1_H002",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0171_G1_H002",
-    "customeridfromheader": "M002",
-    "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
+    "userdata01": "10.1",
+    "userdata02": "V",
+    "userdata12": 1000
    }
   }
  ],
  "触发交易(当前笔)": {
   "apiModel": 20,
-  "bizid": "BIZ_ACQ_RS4_000032_0171",
-  "biztime": "2026-07-29 14:30:00",
-  "policyCode": "Acq_Disputes",
+  "bizid": "BIZ_000032_ROW162_C01",
+  "biztime": "2026-08-07 14:36:15",
+  "policyCode": "Acq_Authorization",
   "appCode": "Acquiring",
   "partnerCode": "kratos",
   "orgCode": "hlb_my",
-  "transactiondate": "2026-07-29",
-  "transactiontime": "14:30:00",
-  "eventtype": "AcqDisputes",
-  "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0171",
-  "customeridfromheader": "M002",
-  "score1": "5999",
-  "customeracctnumber": "5212340000000005",
-  "userdata01": "13.1",
-  "userdata12": 300,
-  "aisopendate": "20260629"
+  "transactiondate": "2026-08-07",
+  "transactiontime": "14:36:15",
+  "externaltransactionid": "EXT_BIZ_000032_ROW162_C01",
+  "merchantid": "M000162",
+  "merchantname": "MERCHANT_TEST",
+  "mcc": "5999",
+  "posentrymode": "C",
+  "transactionamount": 300,
+  "transactiontype": "M",
+  "terminalid": "T000162",
+  "userindicator02": "D",
+  "authsecondaryverify": "V",
+  "cvvverifycode": "V",
+  "paymentinstrumentid": "5212340001620000",
+  "customeracctnumber": "5212340001620000",
+  "transactioncategory": "M",
+  "aisopendate": "20260708"
  }
 }</t>
         </is>
       </c>
       <c r="O162" s="38" t="inlineStr">
         <is>
-          <t>阻塞</t>
-        </is>
-      </c>
-      <c r="P162" s="38" t="n"/>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="P162" s="38" t="inlineStr">
+        <is>
+          <t>1786084575000115C267DOR5O7FH3FSHAQY</t>
+        </is>
+      </c>
       <c r="Q162" s="38" t="inlineStr">
         <is>
-          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共3处，旧地址405）；补充aisopendate=20260629（入网天数30天，条件2需成立） || 执行结果：执行阻塞：接口调用成功，但返回未包含目标规则命中证据 返回报文：162_ACQ_RS4_000032_反案例.json</t>
+          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共3处，旧地址405）；补充aisopendate=20260629（入网天数30天，条件2需成立） || 执行结果：目标规则未命中，符合预期 返回报文：162_ACQ_RS4_000032_反案例.json</t>
         </is>
       </c>
     </row>
@@ -34235,150 +34137,77 @@
         <is>
           <t>{
  "说明": "ACQ_RS4_000032_反案例_反向场景 2：商户入网&gt;90天(C2缺) — 反向不触发",
- "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
+ "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
  "历史数据(构造事件历史)": [
   {
    "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
    "时间窗口": "近30天",
-   "请求参数": {
+   "批量生成数量": 4,
+   "账号用商户": true,
+   "字段分布说明": "4笔拒付事件（AcqDisputes，cardscheme=V/reasoncode=10.1），商户维度=customeracctnumber",
+   "请求参数模板": {
+    "method": 20,
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0172_G1_H001",
-    "biztime": "2026-07-28 14:30:00",
+    "bizid": "BIZ_000032_ROW163_H{序号001-099}",
+    "biztime": "2026-08-07 14:31:15",
     "policyCode": "Acq_Disputes",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:31:15",
     "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0172_G1_H001",
-    "customeridfromheader": "M003",
+    "externaltransactionid": "EXT_BIZ_000032_ROW163_H{序号001-099}",
+    "customeracctnumber": "PLACEHOLDER",
     "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0172_G1_H002",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0172_G1_H002",
-    "customeridfromheader": "M003",
-    "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0172_G1_H003",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0172_G1_H003",
-    "customeridfromheader": "M003",
-    "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0172_G1_H004",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0172_G1_H004",
-    "customeridfromheader": "M003",
-    "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000032_0172_G1_H005",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0172_G1_H005",
-    "customeridfromheader": "M003",
-    "score1": "5999",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 300
+    "userdata01": "10.1",
+    "userdata02": "V",
+    "userdata12": 1000
    }
   }
  ],
  "触发交易(当前笔)": {
   "apiModel": 20,
-  "bizid": "BIZ_ACQ_RS4_000032_0172",
-  "biztime": "2026-07-29 14:30:00",
-  "policyCode": "Acq_Disputes",
+  "bizid": "BIZ_000032_ROW163_C01",
+  "biztime": "2026-08-07 14:36:15",
+  "policyCode": "Acq_Authorization",
   "appCode": "Acquiring",
   "partnerCode": "kratos",
   "orgCode": "hlb_my",
-  "transactiondate": "2026-07-29",
-  "transactiontime": "14:30:00",
-  "eventtype": "AcqDisputes",
-  "externaltransactionid": "EXT_BIZ_ACQ_RS4_000032_0172",
-  "customeridfromheader": "M003",
-  "score1": "5999",
-  "customeracctnumber": "5212340000000005",
-  "userdata01": "13.1",
-  "userdata12": 300,
-  "aisopendate": "20260130"
+  "transactiondate": "2026-08-07",
+  "transactiontime": "14:36:15",
+  "externaltransactionid": "EXT_BIZ_000032_ROW163_C01",
+  "merchantid": "M000163",
+  "merchantname": "MERCHANT_TEST",
+  "mcc": "5999",
+  "posentrymode": "C",
+  "transactionamount": 300,
+  "transactiontype": "M",
+  "terminalid": "T000163",
+  "userindicator02": "D",
+  "authsecondaryverify": "V",
+  "cvvverifycode": "V",
+  "paymentinstrumentid": "5212340001630000",
+  "customeracctnumber": "5212340001630000",
+  "transactioncategory": "M",
+  "aisopendate": "20260208"
  }
 }</t>
         </is>
       </c>
       <c r="O163" s="38" t="inlineStr">
         <is>
-          <t>阻塞</t>
-        </is>
-      </c>
-      <c r="P163" s="38" t="n"/>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="P163" s="38" t="inlineStr">
+        <is>
+          <t>1786084575000115C267DLZWQGEW2T6RWCD</t>
+        </is>
+      </c>
       <c r="Q163" s="38" t="inlineStr">
         <is>
-          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共6处，旧地址405）；补充aisopendate=20260130（入网天数180天，条件2需破坏） || 执行结果：执行阻塞：接口调用成功，但返回未包含目标规则命中证据 返回报文：163_ACQ_RS4_000032_反案例.json</t>
+          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共6处，旧地址405）；补充aisopendate=20260130（入网天数180天，条件2需破坏） || 执行结果：目标规则未命中，符合预期 返回报文：163_ACQ_RS4_000032_反案例.json</t>
         </is>
       </c>
     </row>
@@ -34475,145 +34304,166 @@
         <is>
           <t>{
  "说明": "ACQ_RS4_000033_正案例_商户拒付率&gt;=同MCC*3且销售&gt;=50000 — 正向触发",
- "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
+ "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
  "历史数据(构造事件历史)": [
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
    "时间窗口": "近30天",
-   "请求参数": {
+   "批量生成数量": 60,
+   "字段分布说明": "基准：20商户各3笔×1000销售(MCC5999)",
+   "请求参数模板": {
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0173_G1_H001",
-    "biztime": "2026-07-28 14:30:00",
+    "bizid": "BIZ_ROW164_BASE_S{序号001-999}",
+    "biztime": "2026-08-07 14:43:47",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0173_G1_H001",
-    "merchantid": "M001",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:43:47",
+    "externaltransactionid": "EXT_BIZ_ROW164_BASE_S{序号001-999}",
+    "merchantid": "PLACEHOLDER",
     "merchantname": "MERCHANT_TEST",
-    "mcc": "5411",
+    "mcc": "5999",
     "posentrymode": "C",
-    "transactionamount": 60000,
+    "transactionamount": 1000,
     "transactiontype": "M",
-    "terminalid": "T173",
+    "terminalid": "T_PLACEHOLDER",
     "userindicator02": "D",
     "authsecondaryverify": "V",
     "cvvverifycode": "V",
-    "paymentinstrumentid": "5212340000000005",
-    "customeracctnumber": "5212340000000005",
+    "paymentinstrumentid": "5212349999880001",
+    "customeracctnumber": "5212349999880001",
+    "transactioncategory": "M"
+   },
+   "分散商户": 20
+  },
+  {
+   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
+   "时间窗口": "近30天",
+   "批量生成数量": 20,
+   "字段分布说明": "基准：20商户各1笔×500拒付",
+   "请求参数模板": {
+    "method": 20,
+    "apiModel": 20,
+    "bizid": "BIZ_ROW164_BASED_D{序号001-999}",
+    "biztime": "2026-08-07 14:48:47",
+    "policyCode": "Acq_Disputes",
+    "appCode": "Acquiring",
+    "partnerCode": "kratos",
+    "orgCode": "hlb_my",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:48:47",
+    "eventtype": "AcqDisputes",
+    "externaltransactionid": "EXT_BIZ_ROW164_BASED_D{序号001-999}",
+    "customeracctnumber": "PLACEHOLDER",
+    "score1": "5999",
+    "userdata01": "10.1",
+    "userdata02": "V",
+    "userdata12": 500
+   },
+   "分散商户": 20,
+   "账号用商户": true
+  },
+  {
+   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
+   "时间窗口": "近30天",
+   "批量生成数量": 60,
+   "字段分布说明": "目标商户销售60×1000=60000(≥50000)",
+   "请求参数模板": {
+    "apiModel": 20,
+    "bizid": "BIZ_ROW164_TGT_S{序号001-999}",
+    "biztime": "2026-08-07 14:43:47",
+    "policyCode": "Acq_Authorization",
+    "appCode": "Acquiring",
+    "partnerCode": "kratos",
+    "orgCode": "hlb_my",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:43:47",
+    "externaltransactionid": "EXT_BIZ_ROW164_TGT_S{序号001-999}",
+    "merchantid": "PLACEHOLDER",
+    "merchantname": "MERCHANT_TEST",
+    "mcc": "5999",
+    "posentrymode": "C",
+    "transactionamount": 1000,
+    "transactiontype": "M",
+    "terminalid": "T_PLACEHOLDER",
+    "userindicator02": "D",
+    "authsecondaryverify": "V",
+    "cvvverifycode": "V",
+    "paymentinstrumentid": "5212349999880001",
+    "customeracctnumber": "5212349999880001",
     "transactioncategory": "M"
    }
   },
   {
    "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
    "时间窗口": "近30天",
-   "请求参数": {
+   "批量生成数量": 8,
+   "字段分布说明": "目标商户拒付8×5000=40000，拒付率66%远超MCC均值3倍",
+   "请求参数模板": {
+    "method": 20,
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0173_G2_H001",
-    "biztime": "2026-07-28 14:30:00",
+    "bizid": "BIZ_ROW164_TGTD_D{序号001-999}",
+    "biztime": "2026-08-07 14:48:47",
     "policyCode": "Acq_Disputes",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:48:47",
     "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0173_G2_H001",
-    "customeridfromheader": "M001",
-    "score1": "5411",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 2400
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
-   "批量生成数量": 50,
-   "时间窗口": "近30天",
-   "bizid规则": "BIZ_ACQ_RS4_000033_0173_G3_H001~H050",
-   "字段分布说明": "同MCC其他商户基准销售：50笔合计50000 MYR，MCC=5411",
-   "字段分布": [],
-   "请求参数模板": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0173_G3_H{序号001-050}",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Authorization",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0173_G3_H{序号001-050}",
-    "merchantid": "MCC_BASE_001",
-    "merchantname": "MERCHANT_TEST",
-    "mcc": "5411",
-    "posentrymode": "C",
-    "transactionamount": 1000,
-    "transactiontype": "M",
-    "terminalid": "T173",
-    "userindicator02": "D",
-    "authsecondaryverify": "V",
-    "cvvverifycode": "V",
-    "paymentinstrumentid": "5212340000000005",
-    "customeracctnumber": "5212340000000005",
-    "transactioncategory": "M"
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0173_G4_H001",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0173_G4_H001",
-    "customeridfromheader": "MCC_BASE_001",
-    "score1": "5411",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 500
-   }
+    "externaltransactionid": "EXT_BIZ_ROW164_TGTD_D{序号001-999}",
+    "customeracctnumber": "PLACEHOLDER",
+    "score1": "5999",
+    "userdata01": "10.1",
+    "userdata02": "V",
+    "userdata12": 5000
+   },
+   "账号用商户": true
   }
  ],
  "触发交易(当前笔)": {
   "apiModel": 20,
-  "bizid": "BIZ_ACQ_RS4_000033_0173",
-  "biztime": "2026-07-29 14:30:00",
-  "policyCode": "Acq_Disputes",
+  "bizid": "BIZ_ROW164_C01",
+  "biztime": "2026-08-07 14:53:47",
+  "policyCode": "Acq_Authorization",
   "appCode": "Acquiring",
   "partnerCode": "kratos",
   "orgCode": "hlb_my",
-  "transactiondate": "2026-07-29",
-  "transactiontime": "14:30:00",
-  "eventtype": "AcqDisputes",
-  "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0173",
-  "customeridfromheader": "M001",
-  "score1": "5411",
-  "customeracctnumber": "5212340000000005",
-  "userdata01": "13.1",
-  "userdata12": 300
+  "transactiondate": "2026-08-07",
+  "transactiontime": "14:53:47",
+  "externaltransactionid": "EXT_BIZ_ROW164_C01",
+  "merchantid": "M000164",
+  "merchantname": "MERCHANT_TEST",
+  "mcc": "5999",
+  "posentrymode": "C",
+  "transactionamount": 300,
+  "transactiontype": "M",
+  "terminalid": "T000164",
+  "userindicator02": "D",
+  "authsecondaryverify": "V",
+  "cvvverifycode": "V",
+  "paymentinstrumentid": "5212340001640000",
+  "customeracctnumber": "5212340001640000",
+  "transactioncategory": "M"
  }
 }</t>
         </is>
       </c>
       <c r="O164" s="44" t="inlineStr">
         <is>
-          <t>阻塞</t>
-        </is>
-      </c>
-      <c r="P164" s="38" t="n"/>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="P164" s="38" t="inlineStr">
+        <is>
+          <t>1786085627000115C267DDLQXFDAGK6JKLM</t>
+        </is>
+      </c>
       <c r="Q164" s="38" t="inlineStr">
         <is>
-          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共3处，旧地址405） || 执行结果：执行阻塞：接口调用成功，但返回未包含目标规则命中证据 返回报文：164_ACQ_RS4_000033_正案例.json</t>
+          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共3处，旧地址405） || 执行结果：规则未触发，正案例执行失败（命中规则: 无） 返回报文：164_ACQ_RS4_000033_正案例.json</t>
         </is>
       </c>
     </row>
@@ -34708,145 +34558,166 @@
         <is>
           <t>{
  "说明": "ACQ_RS4_000033_反案例_反向场景 1：拒付率不足3倍(C1缺) — 反向不触发",
- "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
+ "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
  "历史数据(构造事件历史)": [
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
    "时间窗口": "近30天",
-   "请求参数": {
+   "批量生成数量": 60,
+   "字段分布说明": "基准：20商户各3笔×1000销售",
+   "请求参数模板": {
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0174_G1_H001",
-    "biztime": "2026-07-28 14:30:00",
+    "bizid": "BIZ_ROW165_BASE_S{序号001-999}",
+    "biztime": "2026-08-07 14:43:47",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0174_G1_H001",
-    "merchantid": "M002",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:43:47",
+    "externaltransactionid": "EXT_BIZ_ROW165_BASE_S{序号001-999}",
+    "merchantid": "PLACEHOLDER",
     "merchantname": "MERCHANT_TEST",
-    "mcc": "5411",
+    "mcc": "5999",
     "posentrymode": "C",
-    "transactionamount": 60000,
+    "transactionamount": 1000,
     "transactiontype": "M",
-    "terminalid": "T174",
+    "terminalid": "T_PLACEHOLDER",
     "userindicator02": "D",
     "authsecondaryverify": "V",
     "cvvverifycode": "V",
-    "paymentinstrumentid": "5212340000000005",
-    "customeracctnumber": "5212340000000005",
+    "paymentinstrumentid": "5212349999880001",
+    "customeracctnumber": "5212349999880001",
+    "transactioncategory": "M"
+   },
+   "分散商户": 20
+  },
+  {
+   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
+   "时间窗口": "近30天",
+   "批量生成数量": 20,
+   "字段分布说明": "基准：20商户各1笔×500拒付",
+   "请求参数模板": {
+    "method": 20,
+    "apiModel": 20,
+    "bizid": "BIZ_ROW165_BASED_D{序号001-999}",
+    "biztime": "2026-08-07 14:48:47",
+    "policyCode": "Acq_Disputes",
+    "appCode": "Acquiring",
+    "partnerCode": "kratos",
+    "orgCode": "hlb_my",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:48:47",
+    "eventtype": "AcqDisputes",
+    "externaltransactionid": "EXT_BIZ_ROW165_BASED_D{序号001-999}",
+    "customeracctnumber": "PLACEHOLDER",
+    "score1": "5999",
+    "userdata01": "10.1",
+    "userdata02": "V",
+    "userdata12": 500
+   },
+   "分散商户": 20,
+   "账号用商户": true
+  },
+  {
+   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
+   "时间窗口": "近30天",
+   "批量生成数量": 60,
+   "字段分布说明": "目标商户销售60×1000=60000",
+   "请求参数模板": {
+    "apiModel": 20,
+    "bizid": "BIZ_ROW165_TGT_S{序号001-999}",
+    "biztime": "2026-08-07 14:43:47",
+    "policyCode": "Acq_Authorization",
+    "appCode": "Acquiring",
+    "partnerCode": "kratos",
+    "orgCode": "hlb_my",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:43:47",
+    "externaltransactionid": "EXT_BIZ_ROW165_TGT_S{序号001-999}",
+    "merchantid": "PLACEHOLDER",
+    "merchantname": "MERCHANT_TEST",
+    "mcc": "5999",
+    "posentrymode": "C",
+    "transactionamount": 1000,
+    "transactiontype": "M",
+    "terminalid": "T_PLACEHOLDER",
+    "userindicator02": "D",
+    "authsecondaryverify": "V",
+    "cvvverifycode": "V",
+    "paymentinstrumentid": "5212349999880001",
+    "customeracctnumber": "5212349999880001",
     "transactioncategory": "M"
    }
   },
   {
    "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
    "时间窗口": "近30天",
-   "请求参数": {
+   "批量生成数量": 1,
+   "字段分布说明": "目标商户拒付1×500，拒付率0.8%未达3倍",
+   "请求参数模板": {
+    "method": 20,
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0174_G2_H001",
-    "biztime": "2026-07-28 14:30:00",
+    "bizid": "BIZ_ROW165_TGTD_D{序号001-999}",
+    "biztime": "2026-08-07 14:48:47",
     "policyCode": "Acq_Disputes",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:48:47",
     "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0174_G2_H001",
-    "customeridfromheader": "M002",
-    "score1": "5411",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 1200
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
-   "批量生成数量": 50,
-   "时间窗口": "近30天",
-   "bizid规则": "BIZ_ACQ_RS4_000033_0174_G3_H001~H050",
-   "字段分布说明": "同MCC其他商户基准销售：50笔合计50000 MYR，MCC=5411",
-   "字段分布": [],
-   "请求参数模板": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0174_G3_H{序号001-050}",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Authorization",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0174_G3_H{序号001-050}",
-    "merchantid": "MCC_BASE_001",
-    "merchantname": "MERCHANT_TEST",
-    "mcc": "5411",
-    "posentrymode": "C",
-    "transactionamount": 1000,
-    "transactiontype": "M",
-    "terminalid": "T174",
-    "userindicator02": "D",
-    "authsecondaryverify": "V",
-    "cvvverifycode": "V",
-    "paymentinstrumentid": "5212340000000005",
-    "customeracctnumber": "5212340000000005",
-    "transactioncategory": "M"
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0174_G4_H001",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0174_G4_H001",
-    "customeridfromheader": "MCC_BASE_001",
-    "score1": "5411",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
+    "externaltransactionid": "EXT_BIZ_ROW165_TGTD_D{序号001-999}",
+    "customeracctnumber": "PLACEHOLDER",
+    "score1": "5999",
+    "userdata01": "10.1",
+    "userdata02": "V",
     "userdata12": 500
-   }
+   },
+   "账号用商户": true
   }
  ],
  "触发交易(当前笔)": {
   "apiModel": 20,
-  "bizid": "BIZ_ACQ_RS4_000033_0174",
-  "biztime": "2026-07-29 14:30:00",
-  "policyCode": "Acq_Disputes",
+  "bizid": "BIZ_ROW165_C01",
+  "biztime": "2026-08-07 14:53:47",
+  "policyCode": "Acq_Authorization",
   "appCode": "Acquiring",
   "partnerCode": "kratos",
   "orgCode": "hlb_my",
-  "transactiondate": "2026-07-29",
-  "transactiontime": "14:30:00",
-  "eventtype": "AcqDisputes",
-  "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0174",
-  "customeridfromheader": "M002",
-  "score1": "5411",
-  "customeracctnumber": "5212340000000005",
-  "userdata01": "13.1",
-  "userdata12": 300
+  "transactiondate": "2026-08-07",
+  "transactiontime": "14:53:47",
+  "externaltransactionid": "EXT_BIZ_ROW165_C01",
+  "merchantid": "M000165",
+  "merchantname": "MERCHANT_TEST",
+  "mcc": "5999",
+  "posentrymode": "C",
+  "transactionamount": 300,
+  "transactiontype": "M",
+  "terminalid": "T000165",
+  "userindicator02": "D",
+  "authsecondaryverify": "V",
+  "cvvverifycode": "V",
+  "paymentinstrumentid": "5212340001650000",
+  "customeracctnumber": "5212340001650000",
+  "transactioncategory": "M"
  }
 }</t>
         </is>
       </c>
       <c r="O165" s="38" t="inlineStr">
         <is>
-          <t>阻塞</t>
-        </is>
-      </c>
-      <c r="P165" s="38" t="n"/>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="P165" s="38" t="inlineStr">
+        <is>
+          <t>1786085627000115C267DV6F1RHCRXZSQZY</t>
+        </is>
+      </c>
       <c r="Q165" s="38" t="inlineStr">
         <is>
-          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共3处，旧地址405） || 执行结果：执行阻塞：接口调用成功，但返回未包含目标规则命中证据 返回报文：165_ACQ_RS4_000033_反案例.json</t>
+          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共3处，旧地址405） || 执行结果：目标规则未命中，符合预期 返回报文：165_ACQ_RS4_000033_反案例.json</t>
         </is>
       </c>
     </row>
@@ -34935,145 +34806,107 @@
         <is>
           <t>{
  "说明": "ACQ_RS4_000033_反案例_反向场景 2：销售金额不足50000(C2缺) — 反向不触发",
- "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
+ "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
  "历史数据(构造事件历史)": [
   {
    "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
    "时间窗口": "近30天",
-   "请求参数": {
+   "批量生成数量": 40,
+   "字段分布说明": "目标商户销售40×1000=40000(&lt;50000)",
+   "请求参数模板": {
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0175_G1_H001",
-    "biztime": "2026-07-28 14:30:00",
+    "bizid": "BIZ_ROW166_TGT_S{序号001-999}",
+    "biztime": "2026-08-07 14:43:47",
     "policyCode": "Acq_Authorization",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0175_G1_H001",
-    "merchantid": "M003",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:43:47",
+    "externaltransactionid": "EXT_BIZ_ROW166_TGT_S{序号001-999}",
+    "merchantid": "PLACEHOLDER",
     "merchantname": "MERCHANT_TEST",
-    "mcc": "5411",
+    "mcc": "5999",
     "posentrymode": "C",
-    "transactionamount": 30000,
+    "transactionamount": 1000,
     "transactiontype": "M",
-    "terminalid": "T175",
+    "terminalid": "T_PLACEHOLDER",
     "userindicator02": "D",
     "authsecondaryverify": "V",
     "cvvverifycode": "V",
-    "paymentinstrumentid": "5212340000000005",
-    "customeracctnumber": "5212340000000005",
+    "paymentinstrumentid": "5212349999880001",
+    "customeracctnumber": "5212349999880001",
     "transactioncategory": "M"
    }
   },
   {
    "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
    "时间窗口": "近30天",
-   "请求参数": {
+   "批量生成数量": 8,
+   "字段分布说明": "目标商户拒付8×5000=40000(高拒付率)",
+   "请求参数模板": {
+    "method": 20,
     "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0175_G2_H001",
-    "biztime": "2026-07-28 14:30:00",
+    "bizid": "BIZ_ROW166_TGTD_D{序号001-999}",
+    "biztime": "2026-08-07 14:48:47",
     "policyCode": "Acq_Disputes",
     "appCode": "Acquiring",
     "partnerCode": "kratos",
     "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
+    "transactiondate": "2026-08-07",
+    "transactiontime": "14:48:47",
     "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0175_G2_H001",
-    "customeridfromheader": "M003",
-    "score1": "5411",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 1200
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/riskService/trade/riskDecision/acqAuthorization",
-   "批量生成数量": 50,
-   "时间窗口": "近30天",
-   "bizid规则": "BIZ_ACQ_RS4_000033_0175_G3_H001~H050",
-   "字段分布说明": "同MCC其他商户基准销售：50笔合计50000 MYR，MCC=5411",
-   "字段分布": [],
-   "请求参数模板": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0175_G3_H{序号001-050}",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Authorization",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0175_G3_H{序号001-050}",
-    "merchantid": "MCC_BASE_001",
-    "merchantname": "MERCHANT_TEST",
-    "mcc": "5411",
-    "posentrymode": "C",
-    "transactionamount": 1000,
-    "transactiontype": "M",
-    "terminalid": "T175",
-    "userindicator02": "D",
-    "authsecondaryverify": "V",
-    "cvvverifycode": "V",
-    "paymentinstrumentid": "5212340000000005",
-    "customeracctnumber": "5212340000000005",
-    "transactioncategory": "M"
-   }
-  },
-  {
-   "接口地址": "http://10.58.17.92:8000/indexApi/salaxyService/acqDisputes/metric",
-   "时间窗口": "近30天",
-   "请求参数": {
-    "apiModel": 20,
-    "bizid": "BIZ_ACQ_RS4_000033_0175_G4_H001",
-    "biztime": "2026-07-28 14:30:00",
-    "policyCode": "Acq_Disputes",
-    "appCode": "Acquiring",
-    "partnerCode": "kratos",
-    "orgCode": "hlb_my",
-    "transactiondate": "2026-07-28",
-    "transactiontime": "14:30:00",
-    "eventtype": "AcqDisputes",
-    "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0175_G4_H001",
-    "customeridfromheader": "MCC_BASE_001",
-    "score1": "5411",
-    "customeracctnumber": "5212340000000005",
-    "userdata01": "13.1",
-    "userdata12": 500
-   }
+    "externaltransactionid": "EXT_BIZ_ROW166_TGTD_D{序号001-999}",
+    "customeracctnumber": "PLACEHOLDER",
+    "score1": "5999",
+    "userdata01": "10.1",
+    "userdata02": "V",
+    "userdata12": 5000
+   },
+   "账号用商户": true
   }
  ],
  "触发交易(当前笔)": {
   "apiModel": 20,
-  "bizid": "BIZ_ACQ_RS4_000033_0175",
-  "biztime": "2026-07-29 14:30:00",
-  "policyCode": "Acq_Disputes",
+  "bizid": "BIZ_ROW166_C01",
+  "biztime": "2026-08-07 14:53:47",
+  "policyCode": "Acq_Authorization",
   "appCode": "Acquiring",
   "partnerCode": "kratos",
   "orgCode": "hlb_my",
-  "transactiondate": "2026-07-29",
-  "transactiontime": "14:30:00",
-  "eventtype": "AcqDisputes",
-  "externaltransactionid": "EXT_BIZ_ACQ_RS4_000033_0175",
-  "customeridfromheader": "M003",
-  "score1": "5411",
-  "customeracctnumber": "5212340000000005",
-  "userdata01": "13.1",
-  "userdata12": 50000
+  "transactiondate": "2026-08-07",
+  "transactiontime": "14:53:47",
+  "externaltransactionid": "EXT_BIZ_ROW166_C01",
+  "merchantid": "M000166",
+  "merchantname": "MERCHANT_TEST",
+  "mcc": "5999",
+  "posentrymode": "C",
+  "transactionamount": 300,
+  "transactiontype": "M",
+  "terminalid": "T000166",
+  "userindicator02": "D",
+  "authsecondaryverify": "V",
+  "cvvverifycode": "V",
+  "paymentinstrumentid": "5212340001660000",
+  "customeracctnumber": "5212340001660000",
+  "transactioncategory": "M"
  }
 }</t>
         </is>
       </c>
       <c r="O166" s="38" t="inlineStr">
         <is>
-          <t>阻塞</t>
-        </is>
-      </c>
-      <c r="P166" s="38" t="n"/>
+          <t>通过</t>
+        </is>
+      </c>
+      <c r="P166" s="38" t="inlineStr">
+        <is>
+          <t>1786085627000115C267DOJNZCHIA3DNO5J</t>
+        </is>
+      </c>
       <c r="Q166" s="38" t="inlineStr">
         <is>
-          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共3处，旧地址405） || 执行结果：执行阻塞：接口调用成功，但返回未包含目标规则命中证据 返回报文：166_ACQ_RS4_000033_反案例.json</t>
+          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共3处，旧地址405） || 执行结果：目标规则未命中，符合预期 返回报文：166_ACQ_RS4_000033_反案例.json</t>
         </is>
       </c>
     </row>

--- a/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
+++ b/日常/2026-08-06/HLB_RS4_规则测试用例_000020+执行结果_20260806.xlsx
@@ -33380,7 +33380,7 @@
       <c r="P158" s="38" t="n"/>
       <c r="Q158" s="38" t="inlineStr">
         <is>
-          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共2处，旧地址405） || 执行结果：执行阻塞：接口调用成功，但返回未包含目标规则命中证据 返回报文：158_ACQ_RS4_000031_正案例.json</t>
+          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共2处，旧地址405） || 执行结果：执行阻塞：接口调用成功，但返回未包含目标规则命中证据 返回报文：158_ACQ_RS4_000031_正案例.json；最终定位(Step0级配置缺陷)：平台AcqDisputes服务CSV确认userdata02(Card Scheme)枚举仅接受V/M，但欺诈类拒付指标的过滤条件写的是Card Scheme=VISA/MasterCard，枚举值与过滤常量对不上→欺诈计数恒为0→C2永不成立。需平台侧修改：把指标过滤里的VISA/MasterCard改成Visa/MC(或V/M)对齐枚举</t>
         </is>
       </c>
     </row>
@@ -34463,7 +34463,7 @@
       </c>
       <c r="Q164" s="38" t="inlineStr">
         <is>
-          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共3处，旧地址405） || 执行结果：规则未触发，正案例执行失败（命中规则: 无） 返回报文：164_ACQ_RS4_000033_正案例.json</t>
+          <t>已修复：acqDisputes地址修正为/indexApi/salaxyService/acqDisputes/metric（共3处，旧地址405） || 执行结果：规则未触发，正案例执行失败（命中规则: 无） 返回报文：164_ACQ_RS4_000033_正案例.json；最终定位(Step0级配置缺陷)：平台AcqDisputes服务CSV确认userdata12实际映射到C_F_TRANSACTIONAMOUNT(交易金额)，但拒付比率指标(m_merchant_chargeback_ratio_30d)分子公式引用的是[字段]Original Txn Amount=C_F_ORIGINALTRXNAMOUNT。该字段在AcqDisputes事件里没映射任何入参→分子恒null→比率恒null→C1无法评估。需平台侧二选一：A) AcqDisputes服务加新入参(如userdata13)映射到C_F_ORIGINALTRXNAMOUNT；B) 改指标分子用C_F_TRANSACTIONAMOUNT</t>
         </is>
       </c>
     </row>
